--- a/research/traditional_assets/database/data/hungary/hungary_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_telecom_services.xlsx
@@ -1376,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1513,22 +1513,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08241197001763827</v>
+        <v>0.08237874924462241</v>
       </c>
       <c r="C2">
-        <v>4147.458184623429</v>
+        <v>4108.017236601419</v>
       </c>
       <c r="D2">
-        <v>4131.858184623428</v>
+        <v>4132.767236601419</v>
       </c>
       <c r="E2">
-        <v>-1121.5</v>
+        <v>-1081.15</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>40.35</v>
       </c>
       <c r="G2">
         <v>15.6</v>
@@ -1549,28 +1549,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.029605</v>
       </c>
       <c r="N2">
-        <v>587.6999999999999</v>
+        <v>585.670395</v>
       </c>
       <c r="O2">
-        <v>52.89299999999999</v>
+        <v>52.71033555</v>
       </c>
       <c r="P2">
-        <v>534.8069999999999</v>
+        <v>532.96005945</v>
       </c>
       <c r="Q2">
-        <v>930.9069999999999</v>
+        <v>929.06005945</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08241197001763827</v>
+        <v>0.08274850428749737</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5376457577663093</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>289.5637328445683</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1595,22 +1595,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08237874924462241</v>
+        <v>0.08234552847160653</v>
       </c>
       <c r="C3">
-        <v>4108.017236601419</v>
+        <v>4068.576688669305</v>
       </c>
       <c r="D3">
-        <v>4132.767236601419</v>
+        <v>4133.676688669305</v>
       </c>
       <c r="E3">
-        <v>-1081.15</v>
+        <v>-1040.8</v>
       </c>
       <c r="F3">
-        <v>40.35</v>
+        <v>80.7</v>
       </c>
       <c r="G3">
         <v>15.6</v>
@@ -1631,28 +1631,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M3">
-        <v>2.029605</v>
+        <v>4.05921</v>
       </c>
       <c r="N3">
-        <v>585.670395</v>
+        <v>583.6407899999999</v>
       </c>
       <c r="O3">
-        <v>52.71033555</v>
+        <v>52.52767109999999</v>
       </c>
       <c r="P3">
-        <v>532.96005945</v>
+        <v>531.1131188999999</v>
       </c>
       <c r="Q3">
-        <v>929.06005945</v>
+        <v>927.2131188999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08274850428749737</v>
+        <v>0.08309190660368013</v>
       </c>
       <c r="T3">
-        <v>0.5376457577663093</v>
+        <v>0.5426426798897647</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>289.5637328445683</v>
+        <v>144.7818664222841</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1677,22 +1677,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08234552847160653</v>
+        <v>0.08231230769859063</v>
       </c>
       <c r="C4">
-        <v>4068.576688669305</v>
+        <v>4029.136541091273</v>
       </c>
       <c r="D4">
-        <v>4133.676688669305</v>
+        <v>4134.586541091273</v>
       </c>
       <c r="E4">
-        <v>-1040.8</v>
+        <v>-1000.45</v>
       </c>
       <c r="F4">
-        <v>80.7</v>
+        <v>121.05</v>
       </c>
       <c r="G4">
         <v>15.6</v>
@@ -1713,28 +1713,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M4">
-        <v>4.05921</v>
+        <v>6.088814999999999</v>
       </c>
       <c r="N4">
-        <v>583.6407899999999</v>
+        <v>581.611185</v>
       </c>
       <c r="O4">
-        <v>52.52767109999999</v>
+        <v>52.34500664999999</v>
       </c>
       <c r="P4">
-        <v>531.1131188999999</v>
+        <v>529.26617835</v>
       </c>
       <c r="Q4">
-        <v>927.2131188999999</v>
+        <v>925.36617835</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08309190660368013</v>
+        <v>0.08344238937999035</v>
       </c>
       <c r="T4">
-        <v>0.5426426798897647</v>
+        <v>0.5477426313353532</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>144.7818664222841</v>
+        <v>96.52124428152277</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1759,22 +1759,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08231230769859063</v>
+        <v>0.08227908692557476</v>
       </c>
       <c r="C5">
-        <v>4029.136541091273</v>
+        <v>3989.696794131741</v>
       </c>
       <c r="D5">
-        <v>4134.586541091273</v>
+        <v>4135.496794131741</v>
       </c>
       <c r="E5">
-        <v>-1000.45</v>
+        <v>-960.1</v>
       </c>
       <c r="F5">
-        <v>121.05</v>
+        <v>161.4</v>
       </c>
       <c r="G5">
         <v>15.6</v>
@@ -1795,28 +1795,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M5">
-        <v>6.088814999999999</v>
+        <v>8.11842</v>
       </c>
       <c r="N5">
-        <v>581.611185</v>
+        <v>579.5815799999999</v>
       </c>
       <c r="O5">
-        <v>52.34500664999999</v>
+        <v>52.16234219999999</v>
       </c>
       <c r="P5">
-        <v>529.26617835</v>
+        <v>527.4192377999999</v>
       </c>
       <c r="Q5">
-        <v>925.36617835</v>
+        <v>923.5192377999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08344238937999035</v>
+        <v>0.08380017388080704</v>
       </c>
       <c r="T5">
-        <v>0.5477426313353532</v>
+        <v>0.5529488317693914</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>96.52124428152277</v>
+        <v>72.39093321114206</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1841,22 +1841,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08227908692557476</v>
+        <v>0.0822458661525589</v>
       </c>
       <c r="C6">
-        <v>3989.696794131741</v>
+        <v>3950.257448055367</v>
       </c>
       <c r="D6">
-        <v>4135.496794131741</v>
+        <v>4136.407448055366</v>
       </c>
       <c r="E6">
-        <v>-960.1</v>
+        <v>-919.75</v>
       </c>
       <c r="F6">
-        <v>161.4</v>
+        <v>201.75</v>
       </c>
       <c r="G6">
         <v>15.6</v>
@@ -1877,28 +1877,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M6">
-        <v>8.11842</v>
+        <v>10.148025</v>
       </c>
       <c r="N6">
-        <v>579.5815799999999</v>
+        <v>577.551975</v>
       </c>
       <c r="O6">
-        <v>52.16234219999999</v>
+        <v>51.97967774999999</v>
       </c>
       <c r="P6">
-        <v>527.4192377999999</v>
+        <v>525.57229725</v>
       </c>
       <c r="Q6">
-        <v>923.5192377999999</v>
+        <v>921.67229725</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08380017388080704</v>
+        <v>0.0841654906869041</v>
       </c>
       <c r="T6">
-        <v>0.5529488317693914</v>
+        <v>0.5582646364230937</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>72.39093321114206</v>
+        <v>57.91274656891366</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1923,22 +1923,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0822458661525589</v>
+        <v>0.08221264537954302</v>
       </c>
       <c r="C7">
-        <v>3950.257448055367</v>
+        <v>3910.818503127034</v>
       </c>
       <c r="D7">
-        <v>4136.407448055366</v>
+        <v>4137.318503127033</v>
       </c>
       <c r="E7">
-        <v>-919.75</v>
+        <v>-879.4</v>
       </c>
       <c r="F7">
-        <v>201.75</v>
+        <v>242.1</v>
       </c>
       <c r="G7">
         <v>15.6</v>
@@ -1959,28 +1959,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M7">
-        <v>10.148025</v>
+        <v>12.17763</v>
       </c>
       <c r="N7">
-        <v>577.551975</v>
+        <v>575.5223699999999</v>
       </c>
       <c r="O7">
-        <v>51.97967774999999</v>
+        <v>51.79701329999999</v>
       </c>
       <c r="P7">
-        <v>525.57229725</v>
+        <v>523.7253566999999</v>
       </c>
       <c r="Q7">
-        <v>921.67229725</v>
+        <v>919.8253566999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0841654906869041</v>
+        <v>0.08453858019100322</v>
       </c>
       <c r="T7">
-        <v>0.5582646364230937</v>
+        <v>0.5636935433034704</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>57.91274656891366</v>
+        <v>48.26062214076137</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2005,22 +2005,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08221264537954302</v>
+        <v>0.08217942460652713</v>
       </c>
       <c r="C8">
-        <v>3910.818503127034</v>
+        <v>3871.379959611864</v>
       </c>
       <c r="D8">
-        <v>4137.318503127033</v>
+        <v>4138.229959611864</v>
       </c>
       <c r="E8">
-        <v>-879.4</v>
+        <v>-839.05</v>
       </c>
       <c r="F8">
-        <v>242.1</v>
+        <v>282.45</v>
       </c>
       <c r="G8">
         <v>15.6</v>
@@ -2041,28 +2041,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M8">
-        <v>12.17763</v>
+        <v>14.207235</v>
       </c>
       <c r="N8">
-        <v>575.5223699999999</v>
+        <v>573.492765</v>
       </c>
       <c r="O8">
-        <v>51.79701329999999</v>
+        <v>51.61434884999999</v>
       </c>
       <c r="P8">
-        <v>523.7253566999999</v>
+        <v>521.87841615</v>
       </c>
       <c r="Q8">
-        <v>919.8253566999999</v>
+        <v>917.97841615</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08453858019100322</v>
+        <v>0.084919693125298</v>
       </c>
       <c r="T8">
-        <v>0.5636935433034704</v>
+        <v>0.5692392008694466</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>48.26062214076138</v>
+        <v>41.36624754922404</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2087,22 +2087,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08217942460652715</v>
+        <v>0.08214620383351127</v>
       </c>
       <c r="C9">
-        <v>3871.379959611864</v>
+        <v>3831.94181777521</v>
       </c>
       <c r="D9">
-        <v>4138.229959611864</v>
+        <v>4139.14181777521</v>
       </c>
       <c r="E9">
-        <v>-839.05</v>
+        <v>-798.7</v>
       </c>
       <c r="F9">
-        <v>282.45</v>
+        <v>322.8</v>
       </c>
       <c r="G9">
         <v>15.6</v>
@@ -2123,28 +2123,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M9">
-        <v>14.207235</v>
+        <v>16.23684</v>
       </c>
       <c r="N9">
-        <v>573.492765</v>
+        <v>571.4631599999999</v>
       </c>
       <c r="O9">
-        <v>51.61434884999999</v>
+        <v>51.43168439999999</v>
       </c>
       <c r="P9">
-        <v>521.87841615</v>
+        <v>520.0314755999999</v>
       </c>
       <c r="Q9">
-        <v>917.97841615</v>
+        <v>916.1314755999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08491969312529801</v>
+        <v>0.08530909112338182</v>
       </c>
       <c r="T9">
-        <v>0.5692392008694467</v>
+        <v>0.5749054162085964</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>41.36624754922403</v>
+        <v>36.19546660557103</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2169,22 +2169,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08214620383351127</v>
+        <v>0.0821129830604954</v>
       </c>
       <c r="C10">
-        <v>3831.94181777521</v>
+        <v>3792.504077882663</v>
       </c>
       <c r="D10">
-        <v>4139.14181777521</v>
+        <v>4140.054077882663</v>
       </c>
       <c r="E10">
-        <v>-798.7</v>
+        <v>-758.35</v>
       </c>
       <c r="F10">
-        <v>322.8</v>
+        <v>363.15</v>
       </c>
       <c r="G10">
         <v>15.6</v>
@@ -2205,28 +2205,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M10">
-        <v>16.23684</v>
+        <v>18.266445</v>
       </c>
       <c r="N10">
-        <v>571.4631599999999</v>
+        <v>569.433555</v>
       </c>
       <c r="O10">
-        <v>51.43168439999999</v>
+        <v>51.24901995</v>
       </c>
       <c r="P10">
-        <v>520.0314755999999</v>
+        <v>518.1845350499999</v>
       </c>
       <c r="Q10">
-        <v>916.1314755999999</v>
+        <v>914.2845350499999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08530909112338182</v>
+        <v>0.08570704731922571</v>
       </c>
       <c r="T10">
-        <v>0.5749054162085964</v>
+        <v>0.580696163753002</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.19546660557103</v>
+        <v>32.17374809384092</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2251,22 +2251,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0821129830604954</v>
+        <v>0.08207976228747954</v>
       </c>
       <c r="C11">
-        <v>3792.504077882663</v>
+        <v>3753.06674020004</v>
       </c>
       <c r="D11">
-        <v>4140.054077882663</v>
+        <v>4140.96674020004</v>
       </c>
       <c r="E11">
-        <v>-758.35</v>
+        <v>-718</v>
       </c>
       <c r="F11">
-        <v>363.15</v>
+        <v>403.4999999999999</v>
       </c>
       <c r="G11">
         <v>15.6</v>
@@ -2287,28 +2287,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M11">
-        <v>18.266445</v>
+        <v>20.29605</v>
       </c>
       <c r="N11">
-        <v>569.433555</v>
+        <v>567.4039499999999</v>
       </c>
       <c r="O11">
-        <v>51.24901995</v>
+        <v>51.06635549999999</v>
       </c>
       <c r="P11">
-        <v>518.1845350499999</v>
+        <v>516.3375944999999</v>
       </c>
       <c r="Q11">
-        <v>914.2845350499999</v>
+        <v>912.4375944999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08570704731922571</v>
+        <v>0.08611384698608837</v>
       </c>
       <c r="T11">
-        <v>0.580696163753002</v>
+        <v>0.5866155945761723</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.17374809384092</v>
+        <v>28.95637328445683</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2333,22 +2333,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08207976228747954</v>
+        <v>0.08204654151446364</v>
       </c>
       <c r="C12">
-        <v>3753.06674020004</v>
+        <v>3713.629804993403</v>
       </c>
       <c r="D12">
-        <v>4140.96674020004</v>
+        <v>4141.879804993403</v>
       </c>
       <c r="E12">
-        <v>-718</v>
+        <v>-677.65</v>
       </c>
       <c r="F12">
-        <v>403.5</v>
+        <v>443.85</v>
       </c>
       <c r="G12">
         <v>15.6</v>
@@ -2369,28 +2369,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M12">
-        <v>20.29605</v>
+        <v>22.325655</v>
       </c>
       <c r="N12">
-        <v>567.4039499999999</v>
+        <v>565.3743449999999</v>
       </c>
       <c r="O12">
-        <v>51.06635549999999</v>
+        <v>50.88369105</v>
       </c>
       <c r="P12">
-        <v>516.3375944999999</v>
+        <v>514.4906539499999</v>
       </c>
       <c r="Q12">
-        <v>912.4375944999999</v>
+        <v>910.5906539499999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08611384698608837</v>
+        <v>0.08652978821849848</v>
       </c>
       <c r="T12">
-        <v>0.5866155945761723</v>
+        <v>0.5926680463167171</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.95637328445683</v>
+        <v>26.32397571314257</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2415,22 +2415,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08204654151446364</v>
+        <v>0.08201332074144776</v>
       </c>
       <c r="C13">
-        <v>3713.629804993403</v>
+        <v>3674.19327252904</v>
       </c>
       <c r="D13">
-        <v>4141.879804993403</v>
+        <v>4142.793272529039</v>
       </c>
       <c r="E13">
-        <v>-677.65</v>
+        <v>-637.3</v>
       </c>
       <c r="F13">
-        <v>443.85</v>
+        <v>484.2</v>
       </c>
       <c r="G13">
         <v>15.6</v>
@@ -2451,28 +2451,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M13">
-        <v>22.325655</v>
+        <v>24.35526</v>
       </c>
       <c r="N13">
-        <v>565.3743449999999</v>
+        <v>563.3447399999999</v>
       </c>
       <c r="O13">
-        <v>50.88369105</v>
+        <v>50.70102659999998</v>
       </c>
       <c r="P13">
-        <v>514.4906539499999</v>
+        <v>512.6437133999999</v>
       </c>
       <c r="Q13">
-        <v>910.5906539499999</v>
+        <v>908.7437133999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08652978821849848</v>
+        <v>0.0869551826607361</v>
       </c>
       <c r="T13">
-        <v>0.5926680463167171</v>
+        <v>0.598858053778638</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.32397571314257</v>
+        <v>24.13031107038069</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08201332074144776</v>
+        <v>0.0819800999684319</v>
       </c>
       <c r="C14">
-        <v>3674.19327252904</v>
+        <v>3634.757143073476</v>
       </c>
       <c r="D14">
-        <v>4142.793272529039</v>
+        <v>4143.707143073476</v>
       </c>
       <c r="E14">
-        <v>-637.3</v>
+        <v>-596.9499999999999</v>
       </c>
       <c r="F14">
-        <v>484.2</v>
+        <v>524.5500000000001</v>
       </c>
       <c r="G14">
         <v>15.6</v>
@@ -2533,28 +2533,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M14">
-        <v>24.35526</v>
+        <v>26.384865</v>
       </c>
       <c r="N14">
-        <v>563.3447399999999</v>
+        <v>561.3151349999999</v>
       </c>
       <c r="O14">
-        <v>50.70102659999998</v>
+        <v>50.51836214999999</v>
       </c>
       <c r="P14">
-        <v>512.6437133999999</v>
+        <v>510.79677285</v>
       </c>
       <c r="Q14">
-        <v>908.7437133999999</v>
+        <v>906.8967728499999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0869551826607361</v>
+        <v>0.08739035628555392</v>
       </c>
       <c r="T14">
-        <v>0.598858053778638</v>
+        <v>0.605190360262672</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.13031107038069</v>
+        <v>22.27413329573602</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2579,22 +2579,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0819800999684319</v>
+        <v>0.08194687919541604</v>
       </c>
       <c r="C15">
-        <v>3634.757143073476</v>
+        <v>3595.321416893474</v>
       </c>
       <c r="D15">
-        <v>4143.707143073476</v>
+        <v>4144.621416893474</v>
       </c>
       <c r="E15">
-        <v>-596.9499999999999</v>
+        <v>-556.5999999999999</v>
       </c>
       <c r="F15">
-        <v>524.5500000000001</v>
+        <v>564.9000000000001</v>
       </c>
       <c r="G15">
         <v>15.6</v>
@@ -2615,28 +2615,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M15">
-        <v>26.384865</v>
+        <v>28.41447</v>
       </c>
       <c r="N15">
-        <v>561.3151349999999</v>
+        <v>559.2855299999999</v>
       </c>
       <c r="O15">
-        <v>50.51836214999999</v>
+        <v>50.33569769999999</v>
       </c>
       <c r="P15">
-        <v>510.79677285</v>
+        <v>508.9498322999999</v>
       </c>
       <c r="Q15">
-        <v>906.8967728499999</v>
+        <v>905.0498322999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08739035628555392</v>
+        <v>0.08783565022722795</v>
       </c>
       <c r="T15">
-        <v>0.605190360262672</v>
+        <v>0.6116699296881952</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.27413329573602</v>
+        <v>20.68312377461201</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2661,22 +2661,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08194687919541604</v>
+        <v>0.08191365842240014</v>
       </c>
       <c r="C16">
-        <v>3595.321416893474</v>
+        <v>3555.886094256033</v>
       </c>
       <c r="D16">
-        <v>4144.621416893474</v>
+        <v>4145.536094256033</v>
       </c>
       <c r="E16">
-        <v>-556.5999999999999</v>
+        <v>-516.2499999999999</v>
       </c>
       <c r="F16">
-        <v>564.9000000000001</v>
+        <v>605.2500000000001</v>
       </c>
       <c r="G16">
         <v>15.6</v>
@@ -2697,28 +2697,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M16">
-        <v>28.41447</v>
+        <v>30.44407500000001</v>
       </c>
       <c r="N16">
-        <v>559.2855299999999</v>
+        <v>557.2559249999999</v>
       </c>
       <c r="O16">
-        <v>50.33569769999999</v>
+        <v>50.15303324999999</v>
       </c>
       <c r="P16">
-        <v>508.9498322999999</v>
+        <v>507.1028917499999</v>
       </c>
       <c r="Q16">
-        <v>905.0498322999999</v>
+        <v>903.2028917499999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08783565022722795</v>
+        <v>0.08829142167341195</v>
       </c>
       <c r="T16">
-        <v>0.6116699296881952</v>
+        <v>0.6183019595707896</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.68312377461201</v>
+        <v>19.30424885630455</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2743,22 +2743,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08191365842240014</v>
+        <v>0.08188043764938428</v>
       </c>
       <c r="C17">
-        <v>3555.886094256033</v>
+        <v>3516.451175428383</v>
       </c>
       <c r="D17">
-        <v>4145.536094256033</v>
+        <v>4146.451175428382</v>
       </c>
       <c r="E17">
-        <v>-516.25</v>
+        <v>-475.9</v>
       </c>
       <c r="F17">
-        <v>605.25</v>
+        <v>645.6</v>
       </c>
       <c r="G17">
         <v>15.6</v>
@@ -2779,28 +2779,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M17">
-        <v>30.444075</v>
+        <v>32.47368</v>
       </c>
       <c r="N17">
-        <v>557.2559249999999</v>
+        <v>555.22632</v>
       </c>
       <c r="O17">
-        <v>50.15303324999999</v>
+        <v>49.9703688</v>
       </c>
       <c r="P17">
-        <v>507.1028917499999</v>
+        <v>505.2559512</v>
       </c>
       <c r="Q17">
-        <v>903.2028917499999</v>
+        <v>901.3559511999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08829142167341195</v>
+        <v>0.08875804482069558</v>
       </c>
       <c r="T17">
-        <v>0.6183019595707896</v>
+        <v>0.625091894926779</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.30424885630455</v>
+        <v>18.09773330278552</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2825,22 +2825,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08188043764938428</v>
+        <v>0.08184721687636841</v>
       </c>
       <c r="C18">
-        <v>3516.451175428383</v>
+        <v>3477.016660677992</v>
       </c>
       <c r="D18">
-        <v>4146.451175428382</v>
+        <v>4147.366660677992</v>
       </c>
       <c r="E18">
-        <v>-475.9</v>
+        <v>-435.55</v>
       </c>
       <c r="F18">
-        <v>645.6</v>
+        <v>685.95</v>
       </c>
       <c r="G18">
         <v>15.6</v>
@@ -2861,28 +2861,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M18">
-        <v>32.47368</v>
+        <v>34.503285</v>
       </c>
       <c r="N18">
-        <v>555.22632</v>
+        <v>553.1967149999999</v>
       </c>
       <c r="O18">
-        <v>49.9703688</v>
+        <v>49.78770434999999</v>
       </c>
       <c r="P18">
-        <v>505.2559512</v>
+        <v>503.4090106499999</v>
       </c>
       <c r="Q18">
-        <v>901.3559511999999</v>
+        <v>899.5090106499999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08875804482069558</v>
+        <v>0.08923591189923905</v>
       </c>
       <c r="T18">
-        <v>0.625091894926779</v>
+        <v>0.6320454431829127</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.09773330278552</v>
+        <v>17.03316075556284</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2907,22 +2907,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08184721687636841</v>
+        <v>0.08181399610335253</v>
       </c>
       <c r="C19">
-        <v>3477.016660677992</v>
+        <v>3437.582550272568</v>
       </c>
       <c r="D19">
-        <v>4147.366660677992</v>
+        <v>4148.282550272568</v>
       </c>
       <c r="E19">
-        <v>-435.55</v>
+        <v>-395.1999999999999</v>
       </c>
       <c r="F19">
-        <v>685.95</v>
+        <v>726.3000000000001</v>
       </c>
       <c r="G19">
         <v>15.6</v>
@@ -2943,28 +2943,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M19">
-        <v>34.503285</v>
+        <v>36.53289</v>
       </c>
       <c r="N19">
-        <v>553.1967149999999</v>
+        <v>551.16711</v>
       </c>
       <c r="O19">
-        <v>49.78770434999999</v>
+        <v>49.60503989999999</v>
       </c>
       <c r="P19">
-        <v>503.4090106499999</v>
+        <v>501.5620701</v>
       </c>
       <c r="Q19">
-        <v>899.5090106499999</v>
+        <v>897.6620700999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08923591189923905</v>
+        <v>0.08972543427238114</v>
       </c>
       <c r="T19">
-        <v>0.6320454431829127</v>
+        <v>0.6391685901770009</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.03316075556284</v>
+        <v>16.08687404692046</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2989,22 +2989,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08181399610335255</v>
+        <v>0.08178077533033666</v>
       </c>
       <c r="C20">
-        <v>3437.582550272567</v>
+        <v>3398.14884448005</v>
       </c>
       <c r="D20">
-        <v>4148.282550272567</v>
+        <v>4149.19884448005</v>
       </c>
       <c r="E20">
-        <v>-395.2</v>
+        <v>-354.85</v>
       </c>
       <c r="F20">
-        <v>726.3</v>
+        <v>766.65</v>
       </c>
       <c r="G20">
         <v>15.6</v>
@@ -3025,28 +3025,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M20">
-        <v>36.53288999999999</v>
+        <v>38.562495</v>
       </c>
       <c r="N20">
-        <v>551.16711</v>
+        <v>549.1375049999999</v>
       </c>
       <c r="O20">
-        <v>49.60503989999999</v>
+        <v>49.42237544999999</v>
       </c>
       <c r="P20">
-        <v>501.5620701</v>
+        <v>499.7151295499999</v>
       </c>
       <c r="Q20">
-        <v>897.6620700999999</v>
+        <v>895.8151295499999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08972543427238114</v>
+        <v>0.09022704361769958</v>
       </c>
       <c r="T20">
-        <v>0.6391685901770009</v>
+        <v>0.6464676173437827</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.08687404692046</v>
+        <v>15.24019646550359</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3071,22 +3071,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08178077533033666</v>
+        <v>0.08174755455732077</v>
       </c>
       <c r="C21">
-        <v>3398.14884448005</v>
+        <v>3358.715543568616</v>
       </c>
       <c r="D21">
-        <v>4149.19884448005</v>
+        <v>4150.115543568616</v>
       </c>
       <c r="E21">
-        <v>-354.85</v>
+        <v>-314.5</v>
       </c>
       <c r="F21">
-        <v>766.65</v>
+        <v>807</v>
       </c>
       <c r="G21">
         <v>15.6</v>
@@ -3107,28 +3107,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M21">
-        <v>38.562495</v>
+        <v>40.59209999999999</v>
       </c>
       <c r="N21">
-        <v>549.1375049999999</v>
+        <v>547.1079</v>
       </c>
       <c r="O21">
-        <v>49.42237544999999</v>
+        <v>49.23971099999999</v>
       </c>
       <c r="P21">
-        <v>499.7151295499999</v>
+        <v>497.868189</v>
       </c>
       <c r="Q21">
-        <v>895.8151295499999</v>
+        <v>893.9681889999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09022704361769958</v>
+        <v>0.09074119319665097</v>
       </c>
       <c r="T21">
-        <v>0.6464676173437827</v>
+        <v>0.6539491201897339</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.24019646550359</v>
+        <v>14.47818664222842</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3153,22 +3153,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08174755455732077</v>
+        <v>0.0817143337843049</v>
       </c>
       <c r="C22">
-        <v>3358.715543568616</v>
+        <v>3319.282647806684</v>
       </c>
       <c r="D22">
-        <v>4150.115543568616</v>
+        <v>4151.032647806684</v>
       </c>
       <c r="E22">
-        <v>-314.5</v>
+        <v>-274.1499999999999</v>
       </c>
       <c r="F22">
-        <v>807</v>
+        <v>847.3500000000001</v>
       </c>
       <c r="G22">
         <v>15.6</v>
@@ -3189,28 +3189,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M22">
-        <v>40.59209999999999</v>
+        <v>42.62170500000001</v>
       </c>
       <c r="N22">
-        <v>547.1079</v>
+        <v>545.0782949999999</v>
       </c>
       <c r="O22">
-        <v>49.23971099999999</v>
+        <v>49.05704654999999</v>
       </c>
       <c r="P22">
-        <v>497.868189</v>
+        <v>496.0212484499999</v>
       </c>
       <c r="Q22">
-        <v>893.9681889999999</v>
+        <v>892.1212484499999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09074119319665097</v>
+        <v>0.09126835922063911</v>
       </c>
       <c r="T22">
-        <v>0.6539491201897339</v>
+        <v>0.6616200281710257</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.47818664222842</v>
+        <v>13.78874918307468</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3235,22 +3235,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0817143337843049</v>
+        <v>0.08168111301128902</v>
       </c>
       <c r="C23">
-        <v>3319.282647806684</v>
+        <v>3279.850157462904</v>
       </c>
       <c r="D23">
-        <v>4151.032647806684</v>
+        <v>4151.950157462904</v>
       </c>
       <c r="E23">
-        <v>-274.15</v>
+        <v>-233.8</v>
       </c>
       <c r="F23">
-        <v>847.35</v>
+        <v>887.7</v>
       </c>
       <c r="G23">
         <v>15.6</v>
@@ -3271,28 +3271,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M23">
-        <v>42.621705</v>
+        <v>44.65131</v>
       </c>
       <c r="N23">
-        <v>545.0782949999999</v>
+        <v>543.04869</v>
       </c>
       <c r="O23">
-        <v>49.05704654999999</v>
+        <v>48.8743821</v>
       </c>
       <c r="P23">
-        <v>496.0212484499999</v>
+        <v>494.1743079</v>
       </c>
       <c r="Q23">
-        <v>892.1212484499999</v>
+        <v>890.2743078999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09126835922063911</v>
+        <v>0.09180904232216541</v>
       </c>
       <c r="T23">
-        <v>0.6616200281710257</v>
+        <v>0.6694876261005558</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.78874918307468</v>
+        <v>13.16198785657128</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3317,22 +3317,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08168111301128902</v>
+        <v>0.08196184223827316</v>
       </c>
       <c r="C24">
-        <v>3279.850157462904</v>
+        <v>3231.759566841657</v>
       </c>
       <c r="D24">
-        <v>4151.950157462904</v>
+        <v>4144.209566841657</v>
       </c>
       <c r="E24">
-        <v>-233.8</v>
+        <v>-193.4499999999999</v>
       </c>
       <c r="F24">
-        <v>887.7</v>
+        <v>928.0500000000001</v>
       </c>
       <c r="G24">
         <v>15.6</v>
@@ -3353,45 +3353,45 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M24">
-        <v>44.65131</v>
+        <v>48.07299</v>
       </c>
       <c r="N24">
-        <v>543.04869</v>
+        <v>539.6270099999999</v>
       </c>
       <c r="O24">
-        <v>48.8743821</v>
+        <v>48.56643089999999</v>
       </c>
       <c r="P24">
-        <v>494.1743079</v>
+        <v>491.0605790999999</v>
       </c>
       <c r="Q24">
-        <v>890.2743078999999</v>
+        <v>887.1605790999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09180904232216541</v>
+        <v>0.09236376914061449</v>
       </c>
       <c r="T24">
-        <v>0.6694876261005558</v>
+        <v>0.6775595772230607</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.09</v>
       </c>
       <c r="W24">
-        <v>0.045773</v>
+        <v>0.047138</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.16198785657128</v>
+        <v>12.22516011589876</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3399,22 +3399,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08196184223827316</v>
+        <v>0.08194227146525729</v>
       </c>
       <c r="C25">
-        <v>3231.759566841657</v>
+        <v>3191.948258779691</v>
       </c>
       <c r="D25">
-        <v>4144.209566841657</v>
+        <v>4144.74825877969</v>
       </c>
       <c r="E25">
-        <v>-193.4499999999999</v>
+        <v>-153.0999999999999</v>
       </c>
       <c r="F25">
-        <v>928.0500000000001</v>
+        <v>968.4000000000001</v>
       </c>
       <c r="G25">
         <v>15.6</v>
@@ -3435,28 +3435,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M25">
-        <v>48.07299</v>
+        <v>50.16312000000001</v>
       </c>
       <c r="N25">
-        <v>539.6270099999999</v>
+        <v>537.5368799999999</v>
       </c>
       <c r="O25">
-        <v>48.56643089999999</v>
+        <v>48.37831919999999</v>
       </c>
       <c r="P25">
-        <v>491.0605790999999</v>
+        <v>489.1585607999999</v>
       </c>
       <c r="Q25">
-        <v>887.1605790999999</v>
+        <v>885.2585607999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09236376914061449</v>
+        <v>0.09293309403323327</v>
       </c>
       <c r="T25">
-        <v>0.6775595772230607</v>
+        <v>0.6858439481119474</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.22516011589876</v>
+        <v>11.71577844440298</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3481,22 +3481,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08194227146525729</v>
+        <v>0.0819227006922414</v>
       </c>
       <c r="C26">
-        <v>3191.948258779691</v>
+        <v>3152.137090781457</v>
       </c>
       <c r="D26">
-        <v>4144.74825877969</v>
+        <v>4145.287090781457</v>
       </c>
       <c r="E26">
-        <v>-153.1</v>
+        <v>-112.75</v>
       </c>
       <c r="F26">
-        <v>968.4</v>
+        <v>1008.75</v>
       </c>
       <c r="G26">
         <v>15.6</v>
@@ -3517,28 +3517,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M26">
-        <v>50.16312</v>
+        <v>52.25325</v>
       </c>
       <c r="N26">
-        <v>537.5368799999999</v>
+        <v>535.44675</v>
       </c>
       <c r="O26">
-        <v>48.37831919999999</v>
+        <v>48.19020749999999</v>
       </c>
       <c r="P26">
-        <v>489.1585607999999</v>
+        <v>487.2565425</v>
       </c>
       <c r="Q26">
-        <v>885.2585607999999</v>
+        <v>883.3565424999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09293309403323327</v>
+        <v>0.09351760092298854</v>
       </c>
       <c r="T26">
-        <v>0.6858439481119473</v>
+        <v>0.6943492355578709</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.71577844440298</v>
+        <v>11.24714730662686</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0819227006922414</v>
+        <v>0.08190312991922553</v>
       </c>
       <c r="C27">
-        <v>3152.137090781457</v>
+        <v>3112.326062901588</v>
       </c>
       <c r="D27">
-        <v>4145.287090781457</v>
+        <v>4145.826062901588</v>
       </c>
       <c r="E27">
-        <v>-112.75</v>
+        <v>-72.39999999999986</v>
       </c>
       <c r="F27">
-        <v>1008.75</v>
+        <v>1049.1</v>
       </c>
       <c r="G27">
         <v>15.6</v>
@@ -3599,28 +3599,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M27">
-        <v>52.25325</v>
+        <v>54.34338</v>
       </c>
       <c r="N27">
-        <v>535.44675</v>
+        <v>533.3566199999999</v>
       </c>
       <c r="O27">
-        <v>48.19020749999999</v>
+        <v>48.00209579999999</v>
       </c>
       <c r="P27">
-        <v>487.2565425</v>
+        <v>485.3545241999999</v>
       </c>
       <c r="Q27">
-        <v>883.3565424999999</v>
+        <v>881.4545241999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09351760092298854</v>
+        <v>0.09411790529625072</v>
       </c>
       <c r="T27">
-        <v>0.6943492355578709</v>
+        <v>0.7030843956374681</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.24714730662686</v>
+        <v>10.81456471791044</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3645,22 +3645,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08190312991922553</v>
+        <v>0.08188355914620966</v>
       </c>
       <c r="C28">
-        <v>3112.326062901588</v>
+        <v>3072.515175194747</v>
       </c>
       <c r="D28">
-        <v>4145.826062901588</v>
+        <v>4146.365175194746</v>
       </c>
       <c r="E28">
-        <v>-72.39999999999986</v>
+        <v>-32.04999999999995</v>
       </c>
       <c r="F28">
-        <v>1049.1</v>
+        <v>1089.45</v>
       </c>
       <c r="G28">
         <v>15.6</v>
@@ -3681,28 +3681,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M28">
-        <v>54.34338</v>
+        <v>56.43351</v>
       </c>
       <c r="N28">
-        <v>533.3566199999999</v>
+        <v>531.26649</v>
       </c>
       <c r="O28">
-        <v>48.00209579999999</v>
+        <v>47.8139841</v>
       </c>
       <c r="P28">
-        <v>485.3545241999999</v>
+        <v>483.4525059</v>
       </c>
       <c r="Q28">
-        <v>881.4545241999999</v>
+        <v>879.5525059</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09411790529625072</v>
+        <v>0.09473465636467077</v>
       </c>
       <c r="T28">
-        <v>0.7030843956374681</v>
+        <v>0.7120588751713008</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.81456471791044</v>
+        <v>10.41402528391376</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3727,22 +3727,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08188355914620966</v>
+        <v>0.08186398837319378</v>
       </c>
       <c r="C29">
-        <v>3072.515175194747</v>
+        <v>3032.704427715624</v>
       </c>
       <c r="D29">
-        <v>4146.365175194746</v>
+        <v>4146.904427715624</v>
       </c>
       <c r="E29">
-        <v>-32.04999999999995</v>
+        <v>8.300000000000182</v>
       </c>
       <c r="F29">
-        <v>1089.45</v>
+        <v>1129.8</v>
       </c>
       <c r="G29">
         <v>15.6</v>
@@ -3763,28 +3763,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M29">
-        <v>56.43351</v>
+        <v>58.52364000000001</v>
       </c>
       <c r="N29">
-        <v>531.26649</v>
+        <v>529.1763599999999</v>
       </c>
       <c r="O29">
-        <v>47.8139841</v>
+        <v>47.62587239999999</v>
       </c>
       <c r="P29">
-        <v>483.4525059</v>
+        <v>481.5504875999999</v>
       </c>
       <c r="Q29">
-        <v>879.5525059</v>
+        <v>877.6504875999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09473465636467077</v>
+        <v>0.0953685394072136</v>
       </c>
       <c r="T29">
-        <v>0.7120588751713008</v>
+        <v>0.7212826458032956</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.41402528391376</v>
+        <v>10.04209580948827</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3809,22 +3809,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08186398837319378</v>
+        <v>0.0822930476001779</v>
       </c>
       <c r="C30">
-        <v>3032.704427715624</v>
+        <v>2980.564221205598</v>
       </c>
       <c r="D30">
-        <v>4146.904427715624</v>
+        <v>4135.114221205597</v>
       </c>
       <c r="E30">
-        <v>8.300000000000182</v>
+        <v>48.65000000000009</v>
       </c>
       <c r="F30">
-        <v>1129.8</v>
+        <v>1170.15</v>
       </c>
       <c r="G30">
         <v>15.6</v>
@@ -3845,45 +3845,45 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M30">
-        <v>58.52364000000001</v>
+        <v>62.603025</v>
       </c>
       <c r="N30">
-        <v>529.1763599999999</v>
+        <v>525.0969749999999</v>
       </c>
       <c r="O30">
-        <v>47.62587239999999</v>
+        <v>47.25872774999999</v>
       </c>
       <c r="P30">
-        <v>481.5504875999999</v>
+        <v>477.8382472499999</v>
       </c>
       <c r="Q30">
-        <v>877.6504875999999</v>
+        <v>873.9382472499999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0953685394072136</v>
+        <v>0.09602027831010973</v>
       </c>
       <c r="T30">
-        <v>0.7212826458032956</v>
+        <v>0.7307662409601353</v>
       </c>
       <c r="U30">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.09</v>
       </c>
       <c r="W30">
-        <v>0.047138</v>
+        <v>0.048685</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>10.04209580948827</v>
+        <v>9.3877252736589</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3891,22 +3891,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0822930476001779</v>
+        <v>0.08228894682716204</v>
       </c>
       <c r="C31">
-        <v>2980.564221205598</v>
+        <v>2940.326589860542</v>
       </c>
       <c r="D31">
-        <v>4135.114221205597</v>
+        <v>4135.226589860542</v>
       </c>
       <c r="E31">
-        <v>48.64999999999986</v>
+        <v>89</v>
       </c>
       <c r="F31">
-        <v>1170.15</v>
+        <v>1210.5</v>
       </c>
       <c r="G31">
         <v>15.6</v>
@@ -3927,28 +3927,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M31">
-        <v>62.60302499999999</v>
+        <v>64.76174999999999</v>
       </c>
       <c r="N31">
-        <v>525.0969749999999</v>
+        <v>522.9382499999999</v>
       </c>
       <c r="O31">
-        <v>47.25872774999999</v>
+        <v>47.06444249999999</v>
       </c>
       <c r="P31">
-        <v>477.8382472499999</v>
+        <v>475.8738074999999</v>
       </c>
       <c r="Q31">
-        <v>873.9382472499999</v>
+        <v>871.9738075</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09602027831010973</v>
+        <v>0.0966906383245172</v>
       </c>
       <c r="T31">
-        <v>0.7307662409601352</v>
+        <v>0.740520795978599</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.387725273658901</v>
+        <v>9.074801097870271</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3973,22 +3973,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08228894682716204</v>
+        <v>0.08228484605414617</v>
       </c>
       <c r="C32">
-        <v>2940.326589860542</v>
+        <v>2900.088964622721</v>
       </c>
       <c r="D32">
-        <v>4135.226589860542</v>
+        <v>4135.338964622721</v>
       </c>
       <c r="E32">
-        <v>89</v>
+        <v>129.3499999999999</v>
       </c>
       <c r="F32">
-        <v>1210.5</v>
+        <v>1250.85</v>
       </c>
       <c r="G32">
         <v>15.6</v>
@@ -4009,28 +4009,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M32">
-        <v>64.76174999999999</v>
+        <v>66.920475</v>
       </c>
       <c r="N32">
-        <v>522.9382499999999</v>
+        <v>520.7795249999999</v>
       </c>
       <c r="O32">
-        <v>47.06444249999999</v>
+        <v>46.87015724999999</v>
       </c>
       <c r="P32">
-        <v>475.8738074999999</v>
+        <v>473.9093677499999</v>
       </c>
       <c r="Q32">
-        <v>871.9738075</v>
+        <v>870.0093677499999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0966906383245172</v>
+        <v>0.09738042906397995</v>
       </c>
       <c r="T32">
-        <v>0.740520795978599</v>
+        <v>0.7505580917222354</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.074801097870271</v>
+        <v>8.782065578584131</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4055,22 +4055,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08228484605414617</v>
+        <v>0.08228074528113029</v>
       </c>
       <c r="C33">
-        <v>2900.088964622721</v>
+        <v>2859.851345492634</v>
       </c>
       <c r="D33">
-        <v>4135.338964622721</v>
+        <v>4135.451345492634</v>
       </c>
       <c r="E33">
-        <v>129.3499999999999</v>
+        <v>169.7</v>
       </c>
       <c r="F33">
-        <v>1250.85</v>
+        <v>1291.2</v>
       </c>
       <c r="G33">
         <v>15.6</v>
@@ -4091,28 +4091,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M33">
-        <v>66.920475</v>
+        <v>69.0792</v>
       </c>
       <c r="N33">
-        <v>520.7795249999999</v>
+        <v>518.6207999999999</v>
       </c>
       <c r="O33">
-        <v>46.87015724999999</v>
+        <v>46.67587199999999</v>
       </c>
       <c r="P33">
-        <v>473.9093677499999</v>
+        <v>471.9449279999999</v>
       </c>
       <c r="Q33">
-        <v>870.0093677499999</v>
+        <v>868.044928</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09738042906397995</v>
+        <v>0.09809050776636807</v>
       </c>
       <c r="T33">
-        <v>0.7505580917222354</v>
+        <v>0.7608906020465671</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.782065578584131</v>
+        <v>8.507626029253377</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4137,22 +4137,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08228074528113029</v>
+        <v>0.08227664450811441</v>
       </c>
       <c r="C34">
-        <v>2859.851345492634</v>
+        <v>2819.613732470777</v>
       </c>
       <c r="D34">
-        <v>4135.451345492634</v>
+        <v>4135.563732470777</v>
       </c>
       <c r="E34">
-        <v>169.7</v>
+        <v>210.05</v>
       </c>
       <c r="F34">
-        <v>1291.2</v>
+        <v>1331.55</v>
       </c>
       <c r="G34">
         <v>15.6</v>
@@ -4173,28 +4173,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M34">
-        <v>69.0792</v>
+        <v>71.23792499999999</v>
       </c>
       <c r="N34">
-        <v>518.6207999999999</v>
+        <v>516.4620749999999</v>
       </c>
       <c r="O34">
-        <v>46.67587199999999</v>
+        <v>46.48158674999999</v>
       </c>
       <c r="P34">
-        <v>471.9449279999999</v>
+        <v>469.9804882499999</v>
       </c>
       <c r="Q34">
-        <v>868.044928</v>
+        <v>866.0804882499999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09809050776636807</v>
+        <v>0.09882178284793197</v>
       </c>
       <c r="T34">
-        <v>0.7608906020465671</v>
+        <v>0.7715315455149088</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.507626029253377</v>
+        <v>8.249819179882063</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4219,22 +4219,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08227664450811441</v>
+        <v>0.08227254373509854</v>
       </c>
       <c r="C35">
-        <v>2819.613732470777</v>
+        <v>2779.376125557651</v>
       </c>
       <c r="D35">
-        <v>4135.563732470777</v>
+        <v>4135.67612555765</v>
       </c>
       <c r="E35">
-        <v>210.05</v>
+        <v>250.4000000000001</v>
       </c>
       <c r="F35">
-        <v>1331.55</v>
+        <v>1371.9</v>
       </c>
       <c r="G35">
         <v>15.6</v>
@@ -4255,28 +4255,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M35">
-        <v>71.23792499999999</v>
+        <v>73.39665000000001</v>
       </c>
       <c r="N35">
-        <v>516.4620749999999</v>
+        <v>514.3033499999999</v>
       </c>
       <c r="O35">
-        <v>46.48158674999999</v>
+        <v>46.28730149999999</v>
       </c>
       <c r="P35">
-        <v>469.9804882499999</v>
+        <v>468.0160484999999</v>
       </c>
       <c r="Q35">
-        <v>866.0804882499999</v>
+        <v>864.1160484999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09882178284793197</v>
+        <v>0.09957521778045234</v>
       </c>
       <c r="T35">
-        <v>0.7715315455149088</v>
+        <v>0.7824949418156244</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.249819179882063</v>
+        <v>8.007177439297296</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4301,22 +4301,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08227254373509854</v>
+        <v>0.08226844296208266</v>
       </c>
       <c r="C36">
-        <v>2779.376125557651</v>
+        <v>2739.138524753751</v>
       </c>
       <c r="D36">
-        <v>4135.67612555765</v>
+        <v>4135.788524753751</v>
       </c>
       <c r="E36">
-        <v>250.4000000000001</v>
+        <v>290.7500000000002</v>
       </c>
       <c r="F36">
-        <v>1371.9</v>
+        <v>1412.25</v>
       </c>
       <c r="G36">
         <v>15.6</v>
@@ -4337,28 +4337,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M36">
-        <v>73.39665000000001</v>
+        <v>75.55537500000001</v>
       </c>
       <c r="N36">
-        <v>514.3033499999999</v>
+        <v>512.1446249999999</v>
       </c>
       <c r="O36">
-        <v>46.28730149999999</v>
+        <v>46.09301624999999</v>
       </c>
       <c r="P36">
-        <v>468.0160484999999</v>
+        <v>466.0516087499999</v>
       </c>
       <c r="Q36">
-        <v>864.1160484999999</v>
+        <v>862.1516087499999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09957521778045234</v>
+        <v>0.100351835326281</v>
       </c>
       <c r="T36">
-        <v>0.7824949418156244</v>
+        <v>0.7937956733871313</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.007177439297296</v>
+        <v>7.778400941031658</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4383,22 +4383,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08226844296208266</v>
+        <v>0.08252642218906678</v>
       </c>
       <c r="C37">
-        <v>2739.138524753751</v>
+        <v>2691.729379668173</v>
       </c>
       <c r="D37">
-        <v>4135.788524753751</v>
+        <v>4128.729379668173</v>
       </c>
       <c r="E37">
-        <v>290.7500000000002</v>
+        <v>331.1000000000001</v>
       </c>
       <c r="F37">
-        <v>1412.25</v>
+        <v>1452.6</v>
       </c>
       <c r="G37">
         <v>15.6</v>
@@ -4419,45 +4419,45 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M37">
-        <v>75.55537500000001</v>
+        <v>78.87618000000001</v>
       </c>
       <c r="N37">
-        <v>512.1446249999999</v>
+        <v>508.82382</v>
       </c>
       <c r="O37">
-        <v>46.09301624999999</v>
+        <v>45.79414379999999</v>
       </c>
       <c r="P37">
-        <v>466.0516087499999</v>
+        <v>463.0296762</v>
       </c>
       <c r="Q37">
-        <v>862.1516087499999</v>
+        <v>859.1296761999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.100351835326281</v>
+        <v>0.1011527221704169</v>
       </c>
       <c r="T37">
-        <v>0.7937956733871313</v>
+        <v>0.8054495528202477</v>
       </c>
       <c r="U37">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V37">
         <v>0.09</v>
       </c>
       <c r="W37">
-        <v>0.048685</v>
+        <v>0.04941300000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y37">
-        <v>7.778400941031658</v>
+        <v>7.450918642358186</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4465,22 +4465,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08252642218906678</v>
+        <v>0.08252960141605092</v>
       </c>
       <c r="C38">
-        <v>2691.729379668174</v>
+        <v>2651.292536058725</v>
       </c>
       <c r="D38">
-        <v>4128.729379668173</v>
+        <v>4128.642536058725</v>
       </c>
       <c r="E38">
-        <v>331.0999999999999</v>
+        <v>371.45</v>
       </c>
       <c r="F38">
-        <v>1452.6</v>
+        <v>1492.95</v>
       </c>
       <c r="G38">
         <v>15.6</v>
@@ -4501,28 +4501,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M38">
-        <v>78.87617999999999</v>
+        <v>81.06718500000001</v>
       </c>
       <c r="N38">
-        <v>508.82382</v>
+        <v>506.6328149999999</v>
       </c>
       <c r="O38">
-        <v>45.79414379999999</v>
+        <v>45.59695334999999</v>
       </c>
       <c r="P38">
-        <v>463.0296762</v>
+        <v>461.03586165</v>
       </c>
       <c r="Q38">
-        <v>859.1296761999999</v>
+        <v>857.1358616499999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1011527221704168</v>
+        <v>0.1019790339937316</v>
       </c>
       <c r="T38">
-        <v>0.8054495528202475</v>
+        <v>0.8174733966798122</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.450918642358188</v>
+        <v>7.249542462834992</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4547,22 +4547,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08252960141605092</v>
+        <v>0.08253278064303504</v>
       </c>
       <c r="C39">
-        <v>2651.292536058725</v>
+        <v>2610.855696102532</v>
       </c>
       <c r="D39">
-        <v>4128.642536058725</v>
+        <v>4128.555696102532</v>
       </c>
       <c r="E39">
-        <v>371.45</v>
+        <v>411.8</v>
       </c>
       <c r="F39">
-        <v>1492.95</v>
+        <v>1533.3</v>
       </c>
       <c r="G39">
         <v>15.6</v>
@@ -4583,28 +4583,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M39">
-        <v>81.06718500000001</v>
+        <v>83.25819</v>
       </c>
       <c r="N39">
-        <v>506.6328149999999</v>
+        <v>504.4418099999999</v>
       </c>
       <c r="O39">
-        <v>45.59695334999999</v>
+        <v>45.39976289999999</v>
       </c>
       <c r="P39">
-        <v>461.03586165</v>
+        <v>459.0420470999999</v>
       </c>
       <c r="Q39">
-        <v>857.1358616499999</v>
+        <v>855.1420470999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1019790339937316</v>
+        <v>0.1028320010371533</v>
       </c>
       <c r="T39">
-        <v>0.8174733966798122</v>
+        <v>0.8298851064703304</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.249542462834992</v>
+        <v>7.058765029602492</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08253278064303504</v>
+        <v>0.08253595987001916</v>
       </c>
       <c r="C40">
-        <v>2610.855696102532</v>
+        <v>2570.418859799368</v>
       </c>
       <c r="D40">
-        <v>4128.555696102532</v>
+        <v>4128.468859799367</v>
       </c>
       <c r="E40">
-        <v>411.8</v>
+        <v>452.1500000000001</v>
       </c>
       <c r="F40">
-        <v>1533.3</v>
+        <v>1573.65</v>
       </c>
       <c r="G40">
         <v>15.6</v>
@@ -4665,28 +4665,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M40">
-        <v>83.25819</v>
+        <v>85.449195</v>
       </c>
       <c r="N40">
-        <v>504.4418099999999</v>
+        <v>502.2508049999999</v>
       </c>
       <c r="O40">
-        <v>45.39976289999999</v>
+        <v>45.20257244999999</v>
       </c>
       <c r="P40">
-        <v>459.0420470999999</v>
+        <v>457.0482325499999</v>
       </c>
       <c r="Q40">
-        <v>855.1420470999999</v>
+        <v>853.1482325499999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1028320010371533</v>
+        <v>0.1037129342131462</v>
       </c>
       <c r="T40">
-        <v>0.8298851064703304</v>
+        <v>0.8427037575654559</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.058765029602492</v>
+        <v>6.877771054484479</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4711,22 +4711,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08253595987001916</v>
+        <v>0.08253913909700331</v>
       </c>
       <c r="C41">
-        <v>2570.418859799368</v>
+        <v>2529.982027148998</v>
       </c>
       <c r="D41">
-        <v>4128.468859799367</v>
+        <v>4128.382027148998</v>
       </c>
       <c r="E41">
-        <v>452.1500000000001</v>
+        <v>492.5</v>
       </c>
       <c r="F41">
-        <v>1573.65</v>
+        <v>1614</v>
       </c>
       <c r="G41">
         <v>15.6</v>
@@ -4747,28 +4747,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M41">
-        <v>85.449195</v>
+        <v>87.64020000000001</v>
       </c>
       <c r="N41">
-        <v>502.2508049999999</v>
+        <v>500.0597999999999</v>
       </c>
       <c r="O41">
-        <v>45.20257244999999</v>
+        <v>45.00538199999999</v>
       </c>
       <c r="P41">
-        <v>457.0482325499999</v>
+        <v>455.0544179999999</v>
       </c>
       <c r="Q41">
-        <v>853.1482325499999</v>
+        <v>851.154418</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1037129342131462</v>
+        <v>0.1046232318283388</v>
       </c>
       <c r="T41">
-        <v>0.8427037575654559</v>
+        <v>0.855949697030419</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.877771054484479</v>
+        <v>6.705826778122367</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4793,22 +4793,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08253913909700331</v>
+        <v>0.08254231832398742</v>
       </c>
       <c r="C42">
-        <v>2529.982027148998</v>
+        <v>2489.545198151192</v>
       </c>
       <c r="D42">
-        <v>4128.382027148998</v>
+        <v>4128.295198151192</v>
       </c>
       <c r="E42">
-        <v>492.5</v>
+        <v>532.8500000000001</v>
       </c>
       <c r="F42">
-        <v>1614</v>
+        <v>1654.35</v>
       </c>
       <c r="G42">
         <v>15.6</v>
@@ -4829,28 +4829,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M42">
-        <v>87.64020000000001</v>
+        <v>89.83120500000001</v>
       </c>
       <c r="N42">
-        <v>500.0597999999999</v>
+        <v>497.8687949999999</v>
       </c>
       <c r="O42">
-        <v>45.00538199999999</v>
+        <v>44.80819154999999</v>
       </c>
       <c r="P42">
-        <v>455.0544179999999</v>
+        <v>453.0606034499999</v>
       </c>
       <c r="Q42">
-        <v>851.154418</v>
+        <v>849.1606034499999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1046232318283388</v>
+        <v>0.1055643869898092</v>
       </c>
       <c r="T42">
-        <v>0.855949697030419</v>
+        <v>0.8696446513924994</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.705826778122367</v>
+        <v>6.542270027436455</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4875,22 +4875,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08254231832398742</v>
+        <v>0.08254549755097154</v>
       </c>
       <c r="C43">
-        <v>2489.545198151192</v>
+        <v>2449.108372805722</v>
       </c>
       <c r="D43">
-        <v>4128.295198151192</v>
+        <v>4128.208372805722</v>
       </c>
       <c r="E43">
-        <v>532.8500000000001</v>
+        <v>573.2000000000003</v>
       </c>
       <c r="F43">
-        <v>1654.35</v>
+        <v>1694.7</v>
       </c>
       <c r="G43">
         <v>15.6</v>
@@ -4911,28 +4911,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M43">
-        <v>89.83120500000001</v>
+        <v>92.02221000000002</v>
       </c>
       <c r="N43">
-        <v>497.8687949999999</v>
+        <v>495.6777899999999</v>
       </c>
       <c r="O43">
-        <v>44.80819154999999</v>
+        <v>44.61100109999999</v>
       </c>
       <c r="P43">
-        <v>453.0606034499999</v>
+        <v>451.0667888999999</v>
       </c>
       <c r="Q43">
-        <v>849.1606034499999</v>
+        <v>847.1667888999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1055643869898092</v>
+        <v>0.1065379957775371</v>
       </c>
       <c r="T43">
-        <v>0.8696446513924994</v>
+        <v>0.8838118455601686</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.542270027436455</v>
+        <v>6.386501693449873</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4957,22 +4957,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08254549755097154</v>
+        <v>0.08254867677795569</v>
       </c>
       <c r="C44">
-        <v>2449.108372805723</v>
+        <v>2408.671551112356</v>
       </c>
       <c r="D44">
-        <v>4128.208372805722</v>
+        <v>4128.121551112356</v>
       </c>
       <c r="E44">
-        <v>573.2</v>
+        <v>613.55</v>
       </c>
       <c r="F44">
-        <v>1694.7</v>
+        <v>1735.05</v>
       </c>
       <c r="G44">
         <v>15.6</v>
@@ -4993,28 +4993,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M44">
-        <v>92.02221</v>
+        <v>94.21321500000001</v>
       </c>
       <c r="N44">
-        <v>495.67779</v>
+        <v>493.4867849999999</v>
       </c>
       <c r="O44">
-        <v>44.6110011</v>
+        <v>44.41381064999999</v>
       </c>
       <c r="P44">
-        <v>451.0667888999999</v>
+        <v>449.0729743499999</v>
       </c>
       <c r="Q44">
-        <v>847.1667889</v>
+        <v>845.17297435</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1065379957775371</v>
+        <v>0.1075457662771152</v>
       </c>
       <c r="T44">
-        <v>0.8838118455601686</v>
+        <v>0.8984761342600367</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.386501693449874</v>
+        <v>6.237978398253365</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5039,22 +5039,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08254867677795569</v>
+        <v>0.0829522560049398</v>
       </c>
       <c r="C45">
-        <v>2408.671551112356</v>
+        <v>2357.329760040986</v>
       </c>
       <c r="D45">
-        <v>4128.121551112356</v>
+        <v>4117.129760040985</v>
       </c>
       <c r="E45">
-        <v>613.55</v>
+        <v>653.9000000000001</v>
       </c>
       <c r="F45">
-        <v>1735.05</v>
+        <v>1775.4</v>
       </c>
       <c r="G45">
         <v>15.6</v>
@@ -5075,45 +5075,45 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M45">
-        <v>94.21321500000001</v>
+        <v>98.17962000000001</v>
       </c>
       <c r="N45">
-        <v>493.4867849999999</v>
+        <v>489.5203799999999</v>
       </c>
       <c r="O45">
-        <v>44.41381064999999</v>
+        <v>44.05683419999999</v>
       </c>
       <c r="P45">
-        <v>449.0729743499999</v>
+        <v>445.4635458</v>
       </c>
       <c r="Q45">
-        <v>845.17297435</v>
+        <v>841.5635457999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1075457662771152</v>
+        <v>0.1085895285802496</v>
       </c>
       <c r="T45">
-        <v>0.8984761342600367</v>
+        <v>0.9136641475563287</v>
       </c>
       <c r="U45">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.09</v>
       </c>
       <c r="W45">
-        <v>0.04941300000000001</v>
+        <v>0.05032300000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>6.237978398253365</v>
+        <v>5.985967352491279</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5121,22 +5121,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0829522560049398</v>
+        <v>0.08296453523192393</v>
       </c>
       <c r="C46">
-        <v>2357.329760040986</v>
+        <v>2316.646243341532</v>
       </c>
       <c r="D46">
-        <v>4117.129760040985</v>
+        <v>4116.796243341531</v>
       </c>
       <c r="E46">
-        <v>653.9000000000001</v>
+        <v>694.25</v>
       </c>
       <c r="F46">
-        <v>1775.4</v>
+        <v>1815.75</v>
       </c>
       <c r="G46">
         <v>15.6</v>
@@ -5157,28 +5157,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M46">
-        <v>98.17962000000001</v>
+        <v>100.410975</v>
       </c>
       <c r="N46">
-        <v>489.5203799999999</v>
+        <v>487.2890249999999</v>
       </c>
       <c r="O46">
-        <v>44.05683419999999</v>
+        <v>43.85601224999999</v>
       </c>
       <c r="P46">
-        <v>445.4635458</v>
+        <v>443.4330127499999</v>
       </c>
       <c r="Q46">
-        <v>841.5635457999999</v>
+        <v>839.5330127499999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1085895285802496</v>
+        <v>0.1096712458762253</v>
       </c>
       <c r="T46">
-        <v>0.9136641475563287</v>
+        <v>0.9294044522452134</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.985967352491279</v>
+        <v>5.852945855769251</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5203,22 +5203,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08296453523192393</v>
+        <v>0.08297681445890806</v>
       </c>
       <c r="C47">
-        <v>2316.646243341532</v>
+        <v>2275.962780672134</v>
       </c>
       <c r="D47">
-        <v>4116.796243341531</v>
+        <v>4116.462780672134</v>
       </c>
       <c r="E47">
-        <v>694.25</v>
+        <v>734.6000000000001</v>
       </c>
       <c r="F47">
-        <v>1815.75</v>
+        <v>1856.1</v>
       </c>
       <c r="G47">
         <v>15.6</v>
@@ -5239,28 +5239,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M47">
-        <v>100.410975</v>
+        <v>102.64233</v>
       </c>
       <c r="N47">
-        <v>487.2890249999999</v>
+        <v>485.0576699999999</v>
       </c>
       <c r="O47">
-        <v>43.85601224999999</v>
+        <v>43.65519029999999</v>
       </c>
       <c r="P47">
-        <v>443.4330127499999</v>
+        <v>441.4024796999999</v>
       </c>
       <c r="Q47">
-        <v>839.5330127499999</v>
+        <v>837.5024796999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1096712458762253</v>
+        <v>0.1107930267757556</v>
       </c>
       <c r="T47">
-        <v>0.9294044522452134</v>
+        <v>0.9457277311818344</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.852945855769251</v>
+        <v>5.725707902382963</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5285,22 +5285,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08297681445890806</v>
+        <v>0.08298909368589219</v>
       </c>
       <c r="C48">
-        <v>2275.962780672134</v>
+        <v>2235.279372019666</v>
       </c>
       <c r="D48">
-        <v>4116.462780672134</v>
+        <v>4116.129372019665</v>
       </c>
       <c r="E48">
-        <v>734.6000000000001</v>
+        <v>774.95</v>
       </c>
       <c r="F48">
-        <v>1856.1</v>
+        <v>1896.45</v>
       </c>
       <c r="G48">
         <v>15.6</v>
@@ -5321,28 +5321,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M48">
-        <v>102.64233</v>
+        <v>104.873685</v>
       </c>
       <c r="N48">
-        <v>485.0576699999999</v>
+        <v>482.8263149999999</v>
       </c>
       <c r="O48">
-        <v>43.65519029999999</v>
+        <v>43.45436834999999</v>
       </c>
       <c r="P48">
-        <v>441.4024796999999</v>
+        <v>439.3719466499999</v>
       </c>
       <c r="Q48">
-        <v>837.5024796999999</v>
+        <v>835.4719466499999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1107930267757556</v>
+        <v>0.1119571390299852</v>
       </c>
       <c r="T48">
-        <v>0.9457277311818344</v>
+        <v>0.9626669829085167</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.725707902382963</v>
+        <v>5.603884329991836</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5367,22 +5367,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08298909368589219</v>
+        <v>0.08300137291287631</v>
       </c>
       <c r="C49">
-        <v>2235.279372019666</v>
+        <v>2194.596017371004</v>
       </c>
       <c r="D49">
-        <v>4116.129372019665</v>
+        <v>4115.796017371003</v>
       </c>
       <c r="E49">
-        <v>774.95</v>
+        <v>815.3000000000002</v>
       </c>
       <c r="F49">
-        <v>1896.45</v>
+        <v>1936.8</v>
       </c>
       <c r="G49">
         <v>15.6</v>
@@ -5403,28 +5403,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M49">
-        <v>104.873685</v>
+        <v>107.10504</v>
       </c>
       <c r="N49">
-        <v>482.8263149999999</v>
+        <v>480.5949599999999</v>
       </c>
       <c r="O49">
-        <v>43.45436834999999</v>
+        <v>43.25354639999999</v>
       </c>
       <c r="P49">
-        <v>439.3719466499999</v>
+        <v>437.3414135999999</v>
       </c>
       <c r="Q49">
-        <v>835.4719466499999</v>
+        <v>833.4414135999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1119571390299852</v>
+        <v>0.1131660248324544</v>
       </c>
       <c r="T49">
-        <v>0.9626669829085167</v>
+        <v>0.9802577443169943</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.603884329991836</v>
+        <v>5.487136739783672</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5449,22 +5449,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08300137291287629</v>
+        <v>0.08301365213986042</v>
       </c>
       <c r="C50">
-        <v>2194.596017371005</v>
+        <v>2153.912716713028</v>
       </c>
       <c r="D50">
-        <v>4115.796017371004</v>
+        <v>4115.462716713027</v>
       </c>
       <c r="E50">
-        <v>815.3</v>
+        <v>855.6499999999999</v>
       </c>
       <c r="F50">
-        <v>1936.8</v>
+        <v>1977.15</v>
       </c>
       <c r="G50">
         <v>15.6</v>
@@ -5485,28 +5485,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M50">
-        <v>107.10504</v>
+        <v>109.336395</v>
       </c>
       <c r="N50">
-        <v>480.5949599999999</v>
+        <v>478.3636049999999</v>
       </c>
       <c r="O50">
-        <v>43.25354639999999</v>
+        <v>43.05272444999999</v>
       </c>
       <c r="P50">
-        <v>437.3414135999999</v>
+        <v>435.31088055</v>
       </c>
       <c r="Q50">
-        <v>833.4414135999999</v>
+        <v>831.41088055</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1131660248324544</v>
+        <v>0.114422317921295</v>
       </c>
       <c r="T50">
-        <v>0.9802577443169942</v>
+        <v>0.9985383395061964</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.487136739783673</v>
+        <v>5.375154357339109</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5531,22 +5531,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08301365213986042</v>
+        <v>0.08302593136684455</v>
       </c>
       <c r="C51">
-        <v>2153.912716713028</v>
+        <v>2113.22947003262</v>
       </c>
       <c r="D51">
-        <v>4115.462716713027</v>
+        <v>4115.12947003262</v>
       </c>
       <c r="E51">
-        <v>855.6499999999999</v>
+        <v>896</v>
       </c>
       <c r="F51">
-        <v>1977.15</v>
+        <v>2017.5</v>
       </c>
       <c r="G51">
         <v>15.6</v>
@@ -5567,28 +5567,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M51">
-        <v>109.336395</v>
+        <v>111.56775</v>
       </c>
       <c r="N51">
-        <v>478.3636049999999</v>
+        <v>476.1322499999999</v>
       </c>
       <c r="O51">
-        <v>43.05272444999999</v>
+        <v>42.85190249999999</v>
       </c>
       <c r="P51">
-        <v>435.31088055</v>
+        <v>433.2803474999999</v>
       </c>
       <c r="Q51">
-        <v>831.41088055</v>
+        <v>829.3803475</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.114422317921295</v>
+        <v>0.1157288627336891</v>
       </c>
       <c r="T51">
-        <v>0.9985383395061964</v>
+        <v>1.017550158502967</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.375154357339109</v>
+        <v>5.267651270192326</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5613,22 +5613,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08302593136684455</v>
+        <v>0.08303821059382867</v>
       </c>
       <c r="C52">
-        <v>2113.22947003262</v>
+        <v>2072.546277316671</v>
       </c>
       <c r="D52">
-        <v>4115.12947003262</v>
+        <v>4114.796277316671</v>
       </c>
       <c r="E52">
-        <v>896</v>
+        <v>936.3499999999999</v>
       </c>
       <c r="F52">
-        <v>2017.5</v>
+        <v>2057.85</v>
       </c>
       <c r="G52">
         <v>15.6</v>
@@ -5649,28 +5649,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M52">
-        <v>111.56775</v>
+        <v>113.799105</v>
       </c>
       <c r="N52">
-        <v>476.1322499999999</v>
+        <v>473.9008949999999</v>
       </c>
       <c r="O52">
-        <v>42.85190249999999</v>
+        <v>42.65108054999999</v>
       </c>
       <c r="P52">
-        <v>433.2803474999999</v>
+        <v>431.2498144499999</v>
       </c>
       <c r="Q52">
-        <v>829.3803475</v>
+        <v>827.3498144499999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1157288627336891</v>
+        <v>0.1170887359057728</v>
       </c>
       <c r="T52">
-        <v>1.017550158502967</v>
+        <v>1.03733797011185</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.267651270192326</v>
+        <v>5.164363990384634</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08303821059382867</v>
+        <v>0.0830504898208128</v>
       </c>
       <c r="C53">
-        <v>2072.546277316671</v>
+        <v>2031.863138552073</v>
       </c>
       <c r="D53">
-        <v>4114.796277316671</v>
+        <v>4114.463138552072</v>
       </c>
       <c r="E53">
-        <v>936.3499999999999</v>
+        <v>976.7000000000003</v>
       </c>
       <c r="F53">
-        <v>2057.85</v>
+        <v>2098.2</v>
       </c>
       <c r="G53">
         <v>15.6</v>
@@ -5731,28 +5731,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M53">
-        <v>113.799105</v>
+        <v>116.03046</v>
       </c>
       <c r="N53">
-        <v>473.9008949999999</v>
+        <v>471.6695399999999</v>
       </c>
       <c r="O53">
-        <v>42.65108054999999</v>
+        <v>42.45025859999999</v>
       </c>
       <c r="P53">
-        <v>431.2498144499999</v>
+        <v>429.2192813999999</v>
       </c>
       <c r="Q53">
-        <v>827.3498144499999</v>
+        <v>825.3192813999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1170887359057728</v>
+        <v>0.1185052704600267</v>
       </c>
       <c r="T53">
-        <v>1.03733797011185</v>
+        <v>1.057950273871104</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.164363990384634</v>
+        <v>5.065049298261852</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5777,22 +5777,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0830504898208128</v>
+        <v>0.08306276904779691</v>
       </c>
       <c r="C54">
-        <v>2031.863138552073</v>
+        <v>1991.180053725724</v>
       </c>
       <c r="D54">
-        <v>4114.463138552072</v>
+        <v>4114.130053725724</v>
       </c>
       <c r="E54">
-        <v>976.7000000000003</v>
+        <v>1017.05</v>
       </c>
       <c r="F54">
-        <v>2098.2</v>
+        <v>2138.55</v>
       </c>
       <c r="G54">
         <v>15.6</v>
@@ -5813,28 +5813,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M54">
-        <v>116.03046</v>
+        <v>118.261815</v>
       </c>
       <c r="N54">
-        <v>471.6695399999999</v>
+        <v>469.4381849999999</v>
       </c>
       <c r="O54">
-        <v>42.45025859999999</v>
+        <v>42.24943664999999</v>
       </c>
       <c r="P54">
-        <v>429.2192813999999</v>
+        <v>427.1887483499999</v>
       </c>
       <c r="Q54">
-        <v>825.3192813999999</v>
+        <v>823.2887483499999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1185052704600267</v>
+        <v>0.119982083080419</v>
       </c>
       <c r="T54">
-        <v>1.057950273871104</v>
+        <v>1.079439696939262</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.065049298261852</v>
+        <v>4.969482330370119</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5859,22 +5859,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08306276904779691</v>
+        <v>0.08307504827478106</v>
       </c>
       <c r="C55">
-        <v>1991.180053725724</v>
+        <v>1950.497022824524</v>
       </c>
       <c r="D55">
-        <v>4114.130053725724</v>
+        <v>4113.797022824524</v>
       </c>
       <c r="E55">
-        <v>1017.05</v>
+        <v>1057.4</v>
       </c>
       <c r="F55">
-        <v>2138.55</v>
+        <v>2178.9</v>
       </c>
       <c r="G55">
         <v>15.6</v>
@@ -5895,28 +5895,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M55">
-        <v>118.261815</v>
+        <v>120.49317</v>
       </c>
       <c r="N55">
-        <v>469.4381849999999</v>
+        <v>467.2068299999999</v>
       </c>
       <c r="O55">
-        <v>42.24943664999999</v>
+        <v>42.04861469999999</v>
       </c>
       <c r="P55">
-        <v>427.1887483499999</v>
+        <v>425.1582152999999</v>
       </c>
       <c r="Q55">
-        <v>823.2887483499999</v>
+        <v>821.2582153</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.119982083080419</v>
+        <v>0.1215231049451762</v>
       </c>
       <c r="T55">
-        <v>1.079439696939262</v>
+        <v>1.101863442749514</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.969482330370119</v>
+        <v>4.87745487980771</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5941,22 +5941,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08307504827478106</v>
+        <v>0.08308732750176517</v>
       </c>
       <c r="C56">
-        <v>1950.497022824524</v>
+        <v>1909.814045835381</v>
       </c>
       <c r="D56">
-        <v>4113.797022824524</v>
+        <v>4113.464045835381</v>
       </c>
       <c r="E56">
-        <v>1057.4</v>
+        <v>1097.75</v>
       </c>
       <c r="F56">
-        <v>2178.9</v>
+        <v>2219.25</v>
       </c>
       <c r="G56">
         <v>15.6</v>
@@ -5977,28 +5977,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M56">
-        <v>120.49317</v>
+        <v>122.724525</v>
       </c>
       <c r="N56">
-        <v>467.2068299999999</v>
+        <v>464.975475</v>
       </c>
       <c r="O56">
-        <v>42.04861469999999</v>
+        <v>41.84779275</v>
       </c>
       <c r="P56">
-        <v>425.1582152999999</v>
+        <v>423.12768225</v>
       </c>
       <c r="Q56">
-        <v>821.2582153</v>
+        <v>819.22768225</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1215231049451762</v>
+        <v>0.1231326166705893</v>
       </c>
       <c r="T56">
-        <v>1.101863442749514</v>
+        <v>1.125283799484666</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.87745487980771</v>
+        <v>4.788773881993024</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6023,22 +6023,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08308732750176517</v>
+        <v>0.0830996067287493</v>
       </c>
       <c r="C57">
-        <v>1909.814045835381</v>
+        <v>1869.131122745202</v>
       </c>
       <c r="D57">
-        <v>4113.464045835381</v>
+        <v>4113.131122745202</v>
       </c>
       <c r="E57">
-        <v>1097.75</v>
+        <v>1138.1</v>
       </c>
       <c r="F57">
-        <v>2219.25</v>
+        <v>2259.6</v>
       </c>
       <c r="G57">
         <v>15.6</v>
@@ -6059,28 +6059,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M57">
-        <v>122.724525</v>
+        <v>124.95588</v>
       </c>
       <c r="N57">
-        <v>464.975475</v>
+        <v>462.7441199999999</v>
       </c>
       <c r="O57">
-        <v>41.84779275</v>
+        <v>41.64697079999999</v>
       </c>
       <c r="P57">
-        <v>423.12768225</v>
+        <v>421.0971491999999</v>
       </c>
       <c r="Q57">
-        <v>819.22768225</v>
+        <v>817.1971491999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1231326166705893</v>
+        <v>0.1248152880198848</v>
       </c>
       <c r="T57">
-        <v>1.125283799484666</v>
+        <v>1.149768717889597</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.788773881993024</v>
+        <v>4.703260062671719</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6105,22 +6105,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0830996067287493</v>
+        <v>0.08311188595573342</v>
       </c>
       <c r="C58">
-        <v>1869.131122745202</v>
+        <v>1828.448253540903</v>
       </c>
       <c r="D58">
-        <v>4113.131122745202</v>
+        <v>4112.798253540903</v>
       </c>
       <c r="E58">
-        <v>1138.1</v>
+        <v>1178.45</v>
       </c>
       <c r="F58">
-        <v>2259.6</v>
+        <v>2299.95</v>
       </c>
       <c r="G58">
         <v>15.6</v>
@@ -6141,28 +6141,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M58">
-        <v>124.95588</v>
+        <v>127.187235</v>
       </c>
       <c r="N58">
-        <v>462.7441199999999</v>
+        <v>460.5127649999999</v>
       </c>
       <c r="O58">
-        <v>41.64697079999999</v>
+        <v>41.44614884999999</v>
       </c>
       <c r="P58">
-        <v>421.0971491999999</v>
+        <v>419.06661615</v>
       </c>
       <c r="Q58">
-        <v>817.1971491999999</v>
+        <v>815.16661615</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1248152880198848</v>
+        <v>0.1265762231528684</v>
       </c>
       <c r="T58">
-        <v>1.149768717889597</v>
+        <v>1.175392469708711</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6179,7 +6179,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.703260062671719</v>
+        <v>4.620746728238883</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6187,22 +6187,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08311188595573342</v>
+        <v>0.08312416518271756</v>
       </c>
       <c r="C59">
-        <v>1828.448253540903</v>
+        <v>1787.765438209402</v>
       </c>
       <c r="D59">
-        <v>4112.798253540903</v>
+        <v>4112.465438209401</v>
       </c>
       <c r="E59">
-        <v>1178.45</v>
+        <v>1218.8</v>
       </c>
       <c r="F59">
-        <v>2299.95</v>
+        <v>2340.3</v>
       </c>
       <c r="G59">
         <v>15.6</v>
@@ -6223,28 +6223,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M59">
-        <v>127.187235</v>
+        <v>129.41859</v>
       </c>
       <c r="N59">
-        <v>460.5127649999999</v>
+        <v>458.2814099999999</v>
       </c>
       <c r="O59">
-        <v>41.44614884999999</v>
+        <v>41.24532689999999</v>
       </c>
       <c r="P59">
-        <v>419.06661615</v>
+        <v>417.0360830999999</v>
       </c>
       <c r="Q59">
-        <v>815.16661615</v>
+        <v>813.1360831</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1265762231528684</v>
+        <v>0.1284210123398037</v>
       </c>
       <c r="T59">
-        <v>1.175392469708711</v>
+        <v>1.202236400185879</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.620746728238883</v>
+        <v>4.541078681200281</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6269,22 +6269,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08312416518271756</v>
+        <v>0.08447869440970168</v>
       </c>
       <c r="C60">
-        <v>1787.765438209402</v>
+        <v>1711.030136166094</v>
       </c>
       <c r="D60">
-        <v>4112.465438209401</v>
+        <v>4076.080136166094</v>
       </c>
       <c r="E60">
-        <v>1218.8</v>
+        <v>1259.15</v>
       </c>
       <c r="F60">
-        <v>2340.3</v>
+        <v>2380.65</v>
       </c>
       <c r="G60">
         <v>15.6</v>
@@ -6305,45 +6305,45 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M60">
-        <v>129.41859</v>
+        <v>137.60157</v>
       </c>
       <c r="N60">
-        <v>458.2814099999999</v>
+        <v>450.0984299999999</v>
       </c>
       <c r="O60">
-        <v>41.24532689999999</v>
+        <v>40.50885869999999</v>
       </c>
       <c r="P60">
-        <v>417.0360830999999</v>
+        <v>409.5895712999999</v>
       </c>
       <c r="Q60">
-        <v>813.1360831</v>
+        <v>805.6895712999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1284210123398037</v>
+        <v>0.1303557912431748</v>
       </c>
       <c r="T60">
-        <v>1.202236400185879</v>
+        <v>1.230389790686323</v>
       </c>
       <c r="U60">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V60">
         <v>0.09</v>
       </c>
       <c r="W60">
-        <v>0.05032300000000001</v>
+        <v>0.05259800000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>4.541078681200282</v>
+        <v>4.271026849475627</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6351,22 +6351,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08447869440970168</v>
+        <v>0.0845137236366858</v>
       </c>
       <c r="C61">
-        <v>1711.030136166094</v>
+        <v>1669.747721163395</v>
       </c>
       <c r="D61">
-        <v>4076.080136166094</v>
+        <v>4075.147721163395</v>
       </c>
       <c r="E61">
-        <v>1259.15</v>
+        <v>1299.5</v>
       </c>
       <c r="F61">
-        <v>2380.65</v>
+        <v>2421</v>
       </c>
       <c r="G61">
         <v>15.6</v>
@@ -6387,28 +6387,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M61">
-        <v>137.60157</v>
+        <v>139.9338</v>
       </c>
       <c r="N61">
-        <v>450.0984299999999</v>
+        <v>447.7661999999999</v>
       </c>
       <c r="O61">
-        <v>40.50885869999999</v>
+        <v>40.29895799999999</v>
       </c>
       <c r="P61">
-        <v>409.5895712999999</v>
+        <v>407.4672419999999</v>
       </c>
       <c r="Q61">
-        <v>805.6895712999999</v>
+        <v>803.567242</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1303557912431748</v>
+        <v>0.1323873090917145</v>
       </c>
       <c r="T61">
-        <v>1.230389790686323</v>
+        <v>1.259950850711789</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.271026849475627</v>
+        <v>4.199843068651033</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6433,22 +6433,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0845137236366858</v>
+        <v>0.08454875286366993</v>
       </c>
       <c r="C62">
-        <v>1669.747721163395</v>
+        <v>1628.465732648339</v>
       </c>
       <c r="D62">
-        <v>4075.147721163395</v>
+        <v>4074.215732648339</v>
       </c>
       <c r="E62">
-        <v>1299.5</v>
+        <v>1339.85</v>
       </c>
       <c r="F62">
-        <v>2421</v>
+        <v>2461.35</v>
       </c>
       <c r="G62">
         <v>15.6</v>
@@ -6469,28 +6469,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M62">
-        <v>139.9338</v>
+        <v>142.26603</v>
       </c>
       <c r="N62">
-        <v>447.7661999999999</v>
+        <v>445.4339699999999</v>
       </c>
       <c r="O62">
-        <v>40.29895799999999</v>
+        <v>40.08905729999999</v>
       </c>
       <c r="P62">
-        <v>407.4672419999999</v>
+        <v>405.3449127</v>
       </c>
       <c r="Q62">
-        <v>803.567242</v>
+        <v>801.4449127</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1323873090917145</v>
+        <v>0.1345230073427434</v>
       </c>
       <c r="T62">
-        <v>1.259950850711789</v>
+        <v>1.291027862533433</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.199843068651033</v>
+        <v>4.130993182279704</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6515,22 +6515,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08454875286366993</v>
+        <v>0.08458378209065405</v>
       </c>
       <c r="C63">
-        <v>1628.465732648339</v>
+        <v>1587.184170328379</v>
       </c>
       <c r="D63">
-        <v>4074.215732648339</v>
+        <v>4073.284170328378</v>
       </c>
       <c r="E63">
-        <v>1339.85</v>
+        <v>1380.2</v>
       </c>
       <c r="F63">
-        <v>2461.35</v>
+        <v>2501.7</v>
       </c>
       <c r="G63">
         <v>15.6</v>
@@ -6551,28 +6551,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M63">
-        <v>142.26603</v>
+        <v>144.59826</v>
       </c>
       <c r="N63">
-        <v>445.4339699999999</v>
+        <v>443.1017399999999</v>
       </c>
       <c r="O63">
-        <v>40.08905729999999</v>
+        <v>39.87915659999999</v>
       </c>
       <c r="P63">
-        <v>405.3449127</v>
+        <v>403.2225834</v>
       </c>
       <c r="Q63">
-        <v>801.4449127</v>
+        <v>799.3225834</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1345230073427434</v>
+        <v>0.1367711107648791</v>
       </c>
       <c r="T63">
-        <v>1.291027862533433</v>
+        <v>1.323740506556216</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.130993182279704</v>
+        <v>4.06436425998487</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6597,22 +6597,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08458378209065405</v>
+        <v>0.08662536131763818</v>
       </c>
       <c r="C64">
-        <v>1587.184170328379</v>
+        <v>1493.266957402942</v>
       </c>
       <c r="D64">
-        <v>4073.284170328378</v>
+        <v>4019.716957402942</v>
       </c>
       <c r="E64">
-        <v>1380.2</v>
+        <v>1420.55</v>
       </c>
       <c r="F64">
-        <v>2501.7</v>
+        <v>2542.05</v>
       </c>
       <c r="G64">
         <v>15.6</v>
@@ -6633,45 +6633,45 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M64">
-        <v>144.59826</v>
+        <v>155.827665</v>
       </c>
       <c r="N64">
-        <v>443.1017399999999</v>
+        <v>431.8723349999999</v>
       </c>
       <c r="O64">
-        <v>39.87915659999999</v>
+        <v>38.86851014999999</v>
       </c>
       <c r="P64">
-        <v>403.2225834</v>
+        <v>393.0038248499999</v>
       </c>
       <c r="Q64">
-        <v>799.3225834</v>
+        <v>789.1038248499999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1367711107648791</v>
+        <v>0.139140733290914</v>
       </c>
       <c r="T64">
-        <v>1.323740506556216</v>
+        <v>1.358221401607257</v>
       </c>
       <c r="U64">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V64">
         <v>0.09</v>
       </c>
       <c r="W64">
-        <v>0.05259800000000001</v>
+        <v>0.055783</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.06436425998487</v>
+        <v>3.77147408324446</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6679,22 +6679,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08662536131763818</v>
+        <v>0.0866922405446223</v>
       </c>
       <c r="C65">
-        <v>1493.266957402942</v>
+        <v>1451.185994475438</v>
       </c>
       <c r="D65">
-        <v>4019.716957402942</v>
+        <v>4017.985994475438</v>
       </c>
       <c r="E65">
-        <v>1420.55</v>
+        <v>1460.9</v>
       </c>
       <c r="F65">
-        <v>2542.05</v>
+        <v>2582.4</v>
       </c>
       <c r="G65">
         <v>15.6</v>
@@ -6715,28 +6715,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M65">
-        <v>155.827665</v>
+        <v>158.30112</v>
       </c>
       <c r="N65">
-        <v>431.8723349999999</v>
+        <v>429.39888</v>
       </c>
       <c r="O65">
-        <v>38.86851014999999</v>
+        <v>38.6458992</v>
       </c>
       <c r="P65">
-        <v>393.0038248499999</v>
+        <v>390.7529808</v>
       </c>
       <c r="Q65">
-        <v>789.1038248499999</v>
+        <v>786.8529808000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.139140733290914</v>
+        <v>0.1416420015128397</v>
       </c>
       <c r="T65">
-        <v>1.358221401607257</v>
+        <v>1.394617901938912</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.77147408324446</v>
+        <v>3.712544800693766</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0866922405446223</v>
+        <v>0.08675911977160644</v>
       </c>
       <c r="C66">
-        <v>1451.185994475438</v>
+        <v>1409.106521674234</v>
       </c>
       <c r="D66">
-        <v>4017.985994475438</v>
+        <v>4016.256521674234</v>
       </c>
       <c r="E66">
-        <v>1460.9</v>
+        <v>1501.25</v>
       </c>
       <c r="F66">
-        <v>2582.4</v>
+        <v>2622.75</v>
       </c>
       <c r="G66">
         <v>15.6</v>
@@ -6797,28 +6797,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M66">
-        <v>158.30112</v>
+        <v>160.774575</v>
       </c>
       <c r="N66">
-        <v>429.39888</v>
+        <v>426.9254249999999</v>
       </c>
       <c r="O66">
-        <v>38.6458992</v>
+        <v>38.42328824999999</v>
       </c>
       <c r="P66">
-        <v>390.7529808</v>
+        <v>388.5021367499999</v>
       </c>
       <c r="Q66">
-        <v>786.8529808000001</v>
+        <v>784.60213675</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1416420015128397</v>
+        <v>0.144286199347447</v>
       </c>
       <c r="T66">
-        <v>1.394617901938912</v>
+        <v>1.433094202289519</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.712544800693766</v>
+        <v>3.655428726836939</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6843,22 +6843,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08675911977160644</v>
+        <v>0.08682599899859056</v>
       </c>
       <c r="C67">
-        <v>1409.106521674234</v>
+        <v>1367.028537075961</v>
       </c>
       <c r="D67">
-        <v>4016.256521674234</v>
+        <v>4014.528537075961</v>
       </c>
       <c r="E67">
-        <v>1501.25</v>
+        <v>1541.6</v>
       </c>
       <c r="F67">
-        <v>2622.75</v>
+        <v>2663.1</v>
       </c>
       <c r="G67">
         <v>15.6</v>
@@ -6879,28 +6879,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M67">
-        <v>160.774575</v>
+        <v>163.24803</v>
       </c>
       <c r="N67">
-        <v>426.9254249999999</v>
+        <v>424.45197</v>
       </c>
       <c r="O67">
-        <v>38.42328824999999</v>
+        <v>38.2006773</v>
       </c>
       <c r="P67">
-        <v>388.5021367499999</v>
+        <v>386.2512927</v>
       </c>
       <c r="Q67">
-        <v>784.60213675</v>
+        <v>782.3512926999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.144286199347447</v>
+        <v>0.1470859382311487</v>
       </c>
       <c r="T67">
-        <v>1.433094202289519</v>
+        <v>1.473833814425455</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.655428726836939</v>
+        <v>3.600043443096985</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6925,22 +6925,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08682599899859056</v>
+        <v>0.08689287822557468</v>
       </c>
       <c r="C68">
-        <v>1367.028537075961</v>
+        <v>1324.952038760558</v>
       </c>
       <c r="D68">
-        <v>4014.528537075961</v>
+        <v>4012.802038760558</v>
       </c>
       <c r="E68">
-        <v>1541.6</v>
+        <v>1581.95</v>
       </c>
       <c r="F68">
-        <v>2663.1</v>
+        <v>2703.45</v>
       </c>
       <c r="G68">
         <v>15.6</v>
@@ -6961,28 +6961,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M68">
-        <v>163.24803</v>
+        <v>165.721485</v>
       </c>
       <c r="N68">
-        <v>424.45197</v>
+        <v>421.9785149999999</v>
       </c>
       <c r="O68">
-        <v>38.2006773</v>
+        <v>37.97806634999999</v>
       </c>
       <c r="P68">
-        <v>386.2512927</v>
+        <v>384.0004486499999</v>
       </c>
       <c r="Q68">
-        <v>782.3512926999999</v>
+        <v>780.1004486499999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1470859382311487</v>
+        <v>0.1500553582593172</v>
       </c>
       <c r="T68">
-        <v>1.473833814425455</v>
+        <v>1.51704249396357</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6999,7 +6999,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.600043443096985</v>
+        <v>3.54631145140897</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7007,22 +7007,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08689287822557468</v>
+        <v>0.0886923974525588</v>
       </c>
       <c r="C69">
-        <v>1324.952038760558</v>
+        <v>1238.698314289529</v>
       </c>
       <c r="D69">
-        <v>4012.802038760558</v>
+        <v>3966.898314289529</v>
       </c>
       <c r="E69">
-        <v>1581.95</v>
+        <v>1622.3</v>
       </c>
       <c r="F69">
-        <v>2703.45</v>
+        <v>2743.8</v>
       </c>
       <c r="G69">
         <v>15.6</v>
@@ -7043,45 +7043,45 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M69">
-        <v>165.721485</v>
+        <v>175.87758</v>
       </c>
       <c r="N69">
-        <v>421.9785149999999</v>
+        <v>411.8224199999999</v>
       </c>
       <c r="O69">
-        <v>37.97806634999999</v>
+        <v>37.06401779999999</v>
       </c>
       <c r="P69">
-        <v>384.0004486499999</v>
+        <v>374.7584021999999</v>
       </c>
       <c r="Q69">
-        <v>780.1004486499999</v>
+        <v>770.8584022</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1500553582593172</v>
+        <v>0.1532103670392463</v>
       </c>
       <c r="T69">
-        <v>1.51704249396357</v>
+        <v>1.562951715972817</v>
       </c>
       <c r="U69">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V69">
         <v>0.09</v>
       </c>
       <c r="W69">
-        <v>0.055783</v>
+        <v>0.05833100000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>3.54631145140897</v>
+        <v>3.341528806571024</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7089,22 +7089,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0886923974525588</v>
+        <v>0.08878475667954294</v>
       </c>
       <c r="C70">
-        <v>1238.698314289529</v>
+        <v>1196.020651047045</v>
       </c>
       <c r="D70">
-        <v>3966.898314289529</v>
+        <v>3964.570651047045</v>
       </c>
       <c r="E70">
-        <v>1622.3</v>
+        <v>1662.65</v>
       </c>
       <c r="F70">
-        <v>2743.8</v>
+        <v>2784.15</v>
       </c>
       <c r="G70">
         <v>15.6</v>
@@ -7125,28 +7125,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M70">
-        <v>175.87758</v>
+        <v>178.464015</v>
       </c>
       <c r="N70">
-        <v>411.8224199999999</v>
+        <v>409.2359849999999</v>
       </c>
       <c r="O70">
-        <v>37.06401779999999</v>
+        <v>36.83123864999999</v>
       </c>
       <c r="P70">
-        <v>374.7584021999999</v>
+        <v>372.4047463499999</v>
       </c>
       <c r="Q70">
-        <v>770.8584022</v>
+        <v>768.50474635</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1532103670392463</v>
+        <v>0.1565689247727192</v>
       </c>
       <c r="T70">
-        <v>1.562951715972817</v>
+        <v>1.611822823272982</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.341528806571024</v>
+        <v>3.293100852852604</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7171,22 +7171,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08878475667954294</v>
+        <v>0.08887711590652707</v>
       </c>
       <c r="C71">
-        <v>1196.020651047045</v>
+        <v>1153.345717816004</v>
       </c>
       <c r="D71">
-        <v>3964.570651047045</v>
+        <v>3962.245717816005</v>
       </c>
       <c r="E71">
-        <v>1662.65</v>
+        <v>1703</v>
       </c>
       <c r="F71">
-        <v>2784.15</v>
+        <v>2824.5</v>
       </c>
       <c r="G71">
         <v>15.6</v>
@@ -7207,28 +7207,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M71">
-        <v>178.464015</v>
+        <v>181.05045</v>
       </c>
       <c r="N71">
-        <v>409.2359849999999</v>
+        <v>406.6495499999999</v>
       </c>
       <c r="O71">
-        <v>36.83123864999999</v>
+        <v>36.59845949999998</v>
       </c>
       <c r="P71">
-        <v>372.4047463499999</v>
+        <v>370.0510904999999</v>
       </c>
       <c r="Q71">
-        <v>768.50474635</v>
+        <v>766.1510904999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1565689247727192</v>
+        <v>0.1601513863550902</v>
       </c>
       <c r="T71">
-        <v>1.611822823272982</v>
+        <v>1.663952004393159</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.293100852852604</v>
+        <v>3.246056554954709</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7253,22 +7253,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08887711590652707</v>
+        <v>0.08896947513351119</v>
       </c>
       <c r="C72">
-        <v>1153.345717816004</v>
+        <v>1110.673509796361</v>
       </c>
       <c r="D72">
-        <v>3962.245717816005</v>
+        <v>3959.923509796361</v>
       </c>
       <c r="E72">
-        <v>1703</v>
+        <v>1743.35</v>
       </c>
       <c r="F72">
-        <v>2824.5</v>
+        <v>2864.85</v>
       </c>
       <c r="G72">
         <v>15.6</v>
@@ -7289,28 +7289,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M72">
-        <v>181.05045</v>
+        <v>183.636885</v>
       </c>
       <c r="N72">
-        <v>406.6495499999999</v>
+        <v>404.0631149999999</v>
       </c>
       <c r="O72">
-        <v>36.59845949999998</v>
+        <v>36.36568034999999</v>
       </c>
       <c r="P72">
-        <v>370.0510904999999</v>
+        <v>367.6974346499999</v>
       </c>
       <c r="Q72">
-        <v>766.1510904999999</v>
+        <v>763.79743465</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1601513863550902</v>
+        <v>0.1639809142534869</v>
       </c>
       <c r="T72">
-        <v>1.663952004393159</v>
+        <v>1.719676301452659</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.246056554954709</v>
+        <v>3.200337448546896</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7335,22 +7335,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08896947513351119</v>
+        <v>0.08906183436049531</v>
       </c>
       <c r="C73">
-        <v>1110.673509796361</v>
+        <v>1068.004022199315</v>
       </c>
       <c r="D73">
-        <v>3959.923509796361</v>
+        <v>3957.604022199315</v>
       </c>
       <c r="E73">
-        <v>1743.35</v>
+        <v>1783.7</v>
       </c>
       <c r="F73">
-        <v>2864.85</v>
+        <v>2905.2</v>
       </c>
       <c r="G73">
         <v>15.6</v>
@@ -7371,28 +7371,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M73">
-        <v>183.636885</v>
+        <v>186.22332</v>
       </c>
       <c r="N73">
-        <v>404.0631149999999</v>
+        <v>401.4766799999999</v>
       </c>
       <c r="O73">
-        <v>36.36568034999999</v>
+        <v>36.13290119999999</v>
       </c>
       <c r="P73">
-        <v>367.6974346499999</v>
+        <v>365.3437787999999</v>
       </c>
       <c r="Q73">
-        <v>763.79743465</v>
+        <v>761.4437788</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1639809142534868</v>
+        <v>0.1680839798589118</v>
       </c>
       <c r="T73">
-        <v>1.719676301452658</v>
+        <v>1.779380905444979</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.200337448546897</v>
+        <v>3.155888317317079</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7417,22 +7417,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08906183436049531</v>
+        <v>0.08915419358747945</v>
       </c>
       <c r="C74">
-        <v>1068.004022199315</v>
+        <v>1025.337250247279</v>
       </c>
       <c r="D74">
-        <v>3957.604022199315</v>
+        <v>3955.287250247279</v>
       </c>
       <c r="E74">
-        <v>1783.7</v>
+        <v>1824.05</v>
       </c>
       <c r="F74">
-        <v>2905.2</v>
+        <v>2945.55</v>
       </c>
       <c r="G74">
         <v>15.6</v>
@@ -7453,28 +7453,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M74">
-        <v>186.22332</v>
+        <v>188.809755</v>
       </c>
       <c r="N74">
-        <v>401.4766799999999</v>
+        <v>398.8902449999999</v>
       </c>
       <c r="O74">
-        <v>36.13290119999999</v>
+        <v>35.90012204999999</v>
       </c>
       <c r="P74">
-        <v>365.3437787999999</v>
+        <v>362.9901229499999</v>
       </c>
       <c r="Q74">
-        <v>761.4437788</v>
+        <v>759.09012295</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1680839798589118</v>
+        <v>0.1724909762499238</v>
       </c>
       <c r="T74">
-        <v>1.779380905444979</v>
+        <v>1.84350807269599</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.155888317317079</v>
+        <v>3.112656970504516</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7499,22 +7499,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08915419358747945</v>
+        <v>0.08924655281446357</v>
       </c>
       <c r="C75">
-        <v>1025.337250247279</v>
+        <v>982.6731891738473</v>
       </c>
       <c r="D75">
-        <v>3955.287250247279</v>
+        <v>3952.973189173847</v>
       </c>
       <c r="E75">
-        <v>1824.05</v>
+        <v>1864.4</v>
       </c>
       <c r="F75">
-        <v>2945.55</v>
+        <v>2985.9</v>
       </c>
       <c r="G75">
         <v>15.6</v>
@@ -7535,28 +7535,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M75">
-        <v>188.809755</v>
+        <v>191.39619</v>
       </c>
       <c r="N75">
-        <v>398.8902449999999</v>
+        <v>396.3038099999999</v>
       </c>
       <c r="O75">
-        <v>35.90012204999999</v>
+        <v>35.66734289999999</v>
       </c>
       <c r="P75">
-        <v>362.9901229499999</v>
+        <v>360.6364670999999</v>
       </c>
       <c r="Q75">
-        <v>759.09012295</v>
+        <v>756.7364670999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1724909762499238</v>
+        <v>0.1772369723633214</v>
       </c>
       <c r="T75">
-        <v>1.84350807269599</v>
+        <v>1.912568098966309</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7573,7 +7573,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.112656970504516</v>
+        <v>3.070594038470671</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7581,22 +7581,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08924655281446357</v>
+        <v>0.0893389120414477</v>
       </c>
       <c r="C76">
-        <v>982.6731891738473</v>
+        <v>940.0118342237624</v>
       </c>
       <c r="D76">
-        <v>3952.973189173847</v>
+        <v>3950.661834223763</v>
       </c>
       <c r="E76">
-        <v>1864.4</v>
+        <v>1904.75</v>
       </c>
       <c r="F76">
-        <v>2985.9</v>
+        <v>3026.25</v>
       </c>
       <c r="G76">
         <v>15.6</v>
@@ -7617,28 +7617,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M76">
-        <v>191.39619</v>
+        <v>193.982625</v>
       </c>
       <c r="N76">
-        <v>396.3038099999999</v>
+        <v>393.7173749999999</v>
       </c>
       <c r="O76">
-        <v>35.66734289999999</v>
+        <v>35.43456375</v>
       </c>
       <c r="P76">
-        <v>360.6364670999999</v>
+        <v>358.28281125</v>
       </c>
       <c r="Q76">
-        <v>756.7364670999999</v>
+        <v>754.38281125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1772369723633214</v>
+        <v>0.1823626481657908</v>
       </c>
       <c r="T76">
-        <v>1.912568098966309</v>
+        <v>1.987152927338255</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.070594038470671</v>
+        <v>3.029652784624396</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7663,22 +7663,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0893389120414477</v>
+        <v>0.09482575126843182</v>
       </c>
       <c r="C77">
-        <v>940.0118342237624</v>
+        <v>767.0370000710095</v>
       </c>
       <c r="D77">
-        <v>3950.661834223763</v>
+        <v>3818.03700007101</v>
       </c>
       <c r="E77">
-        <v>1904.75</v>
+        <v>1945.1</v>
       </c>
       <c r="F77">
-        <v>3026.25</v>
+        <v>3066.6</v>
       </c>
       <c r="G77">
         <v>15.6</v>
@@ -7699,45 +7699,45 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M77">
-        <v>193.982625</v>
+        <v>220.48854</v>
       </c>
       <c r="N77">
-        <v>393.7173749999999</v>
+        <v>367.2114599999999</v>
       </c>
       <c r="O77">
-        <v>35.43456375</v>
+        <v>33.04903139999999</v>
       </c>
       <c r="P77">
-        <v>358.28281125</v>
+        <v>334.1624285999999</v>
       </c>
       <c r="Q77">
-        <v>754.38281125</v>
+        <v>730.2624286</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1823626481657908</v>
+        <v>0.1879154636184659</v>
       </c>
       <c r="T77">
-        <v>1.987152927338255</v>
+        <v>2.067953158074529</v>
       </c>
       <c r="U77">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V77">
         <v>0.09</v>
       </c>
       <c r="W77">
-        <v>0.05833100000000001</v>
+        <v>0.065429</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.029652784624396</v>
+        <v>2.665444653041831</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7745,22 +7745,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09482575126843182</v>
+        <v>0.09498909049541593</v>
       </c>
       <c r="C78">
-        <v>767.0370000710095</v>
+        <v>722.8752046002637</v>
       </c>
       <c r="D78">
-        <v>3818.03700007101</v>
+        <v>3814.225204600264</v>
       </c>
       <c r="E78">
-        <v>1945.1</v>
+        <v>1985.45</v>
       </c>
       <c r="F78">
-        <v>3066.6</v>
+        <v>3106.95</v>
       </c>
       <c r="G78">
         <v>15.6</v>
@@ -7781,28 +7781,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M78">
-        <v>220.48854</v>
+        <v>223.389705</v>
       </c>
       <c r="N78">
-        <v>367.2114599999999</v>
+        <v>364.3102949999999</v>
       </c>
       <c r="O78">
-        <v>33.04903139999999</v>
+        <v>32.78792654999999</v>
       </c>
       <c r="P78">
-        <v>334.1624285999999</v>
+        <v>331.5223684499999</v>
       </c>
       <c r="Q78">
-        <v>730.2624286</v>
+        <v>727.6223684499998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1879154636184659</v>
+        <v>0.193951132588765</v>
       </c>
       <c r="T78">
-        <v>2.067953158074529</v>
+        <v>2.155779495831348</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7819,7 +7819,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.665444653041831</v>
+        <v>2.630828488716612</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7827,22 +7827,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09498909049541593</v>
+        <v>0.09515242972240007</v>
       </c>
       <c r="C79">
-        <v>722.8752046002637</v>
+        <v>678.7210126666996</v>
       </c>
       <c r="D79">
-        <v>3814.225204600264</v>
+        <v>3810.4210126667</v>
       </c>
       <c r="E79">
-        <v>1985.45</v>
+        <v>2025.8</v>
       </c>
       <c r="F79">
-        <v>3106.95</v>
+        <v>3147.3</v>
       </c>
       <c r="G79">
         <v>15.6</v>
@@ -7863,28 +7863,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M79">
-        <v>223.389705</v>
+        <v>226.29087</v>
       </c>
       <c r="N79">
-        <v>364.3102949999999</v>
+        <v>361.4091299999999</v>
       </c>
       <c r="O79">
-        <v>32.78792654999999</v>
+        <v>32.52682169999999</v>
       </c>
       <c r="P79">
-        <v>331.5223684499999</v>
+        <v>328.8823082999999</v>
       </c>
       <c r="Q79">
-        <v>727.6223684499998</v>
+        <v>724.9823082999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.193951132588765</v>
+        <v>0.2005354987381821</v>
       </c>
       <c r="T79">
-        <v>2.155779495831348</v>
+        <v>2.251590046111515</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7901,7 +7901,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.630828488716612</v>
+        <v>2.597099918348451</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7909,22 +7909,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09515242972240007</v>
+        <v>0.09531576894938419</v>
       </c>
       <c r="C80">
-        <v>678.7210126666996</v>
+        <v>634.5744015423779</v>
       </c>
       <c r="D80">
-        <v>3810.4210126667</v>
+        <v>3806.624401542378</v>
       </c>
       <c r="E80">
-        <v>2025.8</v>
+        <v>2066.15</v>
       </c>
       <c r="F80">
-        <v>3147.3</v>
+        <v>3187.65</v>
       </c>
       <c r="G80">
         <v>15.6</v>
@@ -7945,28 +7945,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M80">
-        <v>226.29087</v>
+        <v>229.192035</v>
       </c>
       <c r="N80">
-        <v>361.4091299999999</v>
+        <v>358.5079649999999</v>
       </c>
       <c r="O80">
-        <v>32.52682169999999</v>
+        <v>32.26571684999999</v>
       </c>
       <c r="P80">
-        <v>328.8823082999999</v>
+        <v>326.2422481499999</v>
       </c>
       <c r="Q80">
-        <v>724.9823082999999</v>
+        <v>722.3422481499999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2005354987381821</v>
+        <v>0.20774694737802</v>
       </c>
       <c r="T80">
-        <v>2.251590046111515</v>
+        <v>2.356525410704079</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.597099918348451</v>
+        <v>2.564225235837711</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7991,22 +7991,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09531576894938419</v>
+        <v>0.09547910817636832</v>
       </c>
       <c r="C81">
-        <v>634.5744015423779</v>
+        <v>590.4353485898496</v>
       </c>
       <c r="D81">
-        <v>3806.624401542378</v>
+        <v>3802.83534858985</v>
       </c>
       <c r="E81">
-        <v>2066.15</v>
+        <v>2106.5</v>
       </c>
       <c r="F81">
-        <v>3187.65</v>
+        <v>3228</v>
       </c>
       <c r="G81">
         <v>15.6</v>
@@ -8027,28 +8027,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M81">
-        <v>229.192035</v>
+        <v>232.0932</v>
       </c>
       <c r="N81">
-        <v>358.5079649999999</v>
+        <v>355.6067999999999</v>
       </c>
       <c r="O81">
-        <v>32.26571684999999</v>
+        <v>32.00461199999999</v>
       </c>
       <c r="P81">
-        <v>326.2422481499999</v>
+        <v>323.6021879999999</v>
       </c>
       <c r="Q81">
-        <v>722.3422481499999</v>
+        <v>719.702188</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.20774694737802</v>
+        <v>0.2156795408818416</v>
       </c>
       <c r="T81">
-        <v>2.356525410704079</v>
+        <v>2.471954311755899</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.564225235837711</v>
+        <v>2.532172420389739</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8073,22 +8073,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09547910817636832</v>
+        <v>0.09564244740335243</v>
       </c>
       <c r="C82">
-        <v>590.4353485898496</v>
+        <v>546.3038312617086</v>
       </c>
       <c r="D82">
-        <v>3802.83534858985</v>
+        <v>3799.053831261709</v>
       </c>
       <c r="E82">
-        <v>2106.5</v>
+        <v>2146.85</v>
       </c>
       <c r="F82">
-        <v>3228</v>
+        <v>3268.35</v>
       </c>
       <c r="G82">
         <v>15.6</v>
@@ -8109,28 +8109,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M82">
-        <v>232.0932</v>
+        <v>234.994365</v>
       </c>
       <c r="N82">
-        <v>355.6067999999999</v>
+        <v>352.7056349999999</v>
       </c>
       <c r="O82">
-        <v>32.00461199999999</v>
+        <v>31.74350714999999</v>
       </c>
       <c r="P82">
-        <v>323.6021879999999</v>
+        <v>320.9621278499999</v>
       </c>
       <c r="Q82">
-        <v>719.702188</v>
+        <v>717.06212785</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2156795408818416</v>
+        <v>0.2244471442281708</v>
       </c>
       <c r="T82">
-        <v>2.471954311755899</v>
+        <v>2.599533623444753</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.532172420389739</v>
+        <v>2.500911032483693</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8155,22 +8155,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09564244740335243</v>
+        <v>0.09871596663033658</v>
       </c>
       <c r="C83">
-        <v>546.3038312617086</v>
+        <v>436.1742540244545</v>
       </c>
       <c r="D83">
-        <v>3799.053831261709</v>
+        <v>3729.274254024455</v>
       </c>
       <c r="E83">
-        <v>2146.85</v>
+        <v>2187.2</v>
       </c>
       <c r="F83">
-        <v>3268.35</v>
+        <v>3308.7</v>
       </c>
       <c r="G83">
         <v>15.6</v>
@@ -8191,45 +8191,45 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M83">
-        <v>234.994365</v>
+        <v>250.79946</v>
       </c>
       <c r="N83">
-        <v>352.7056349999999</v>
+        <v>336.9005399999999</v>
       </c>
       <c r="O83">
-        <v>31.74350714999999</v>
+        <v>30.32104859999999</v>
       </c>
       <c r="P83">
-        <v>320.9621278499999</v>
+        <v>306.5794913999999</v>
       </c>
       <c r="Q83">
-        <v>717.06212785</v>
+        <v>702.6794914</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2244471442281708</v>
+        <v>0.2341889257240921</v>
       </c>
       <c r="T83">
-        <v>2.599533623444753</v>
+        <v>2.741288414210146</v>
       </c>
       <c r="U83">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V83">
         <v>0.09</v>
       </c>
       <c r="W83">
-        <v>0.065429</v>
+        <v>0.06897800000000001</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y83">
-        <v>2.500911032483693</v>
+        <v>2.343306480803427</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8237,22 +8237,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09871596663033658</v>
+        <v>0.09891479585732071</v>
       </c>
       <c r="C84">
-        <v>436.1742540244545</v>
+        <v>391.3983115209517</v>
       </c>
       <c r="D84">
-        <v>3729.274254024455</v>
+        <v>3724.848311520952</v>
       </c>
       <c r="E84">
-        <v>2187.2</v>
+        <v>2227.55</v>
       </c>
       <c r="F84">
-        <v>3308.7</v>
+        <v>3349.05</v>
       </c>
       <c r="G84">
         <v>15.6</v>
@@ -8273,28 +8273,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M84">
-        <v>250.79946</v>
+        <v>253.85799</v>
       </c>
       <c r="N84">
-        <v>336.9005399999999</v>
+        <v>333.8420099999999</v>
       </c>
       <c r="O84">
-        <v>30.32104859999999</v>
+        <v>30.04578089999999</v>
       </c>
       <c r="P84">
-        <v>306.5794913999999</v>
+        <v>303.7962290999999</v>
       </c>
       <c r="Q84">
-        <v>702.6794914</v>
+        <v>699.8962290999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2341889257240921</v>
+        <v>0.24507679916071</v>
       </c>
       <c r="T84">
-        <v>2.741288414210146</v>
+        <v>2.899720239183233</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.343306480803427</v>
+        <v>2.315073872600976</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8319,22 +8319,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09891479585732071</v>
+        <v>0.09911362508430482</v>
       </c>
       <c r="C85">
-        <v>391.3983115209517</v>
+        <v>346.6328620758168</v>
       </c>
       <c r="D85">
-        <v>3724.848311520952</v>
+        <v>3720.432862075817</v>
       </c>
       <c r="E85">
-        <v>2227.55</v>
+        <v>2267.900000000001</v>
       </c>
       <c r="F85">
-        <v>3349.05</v>
+        <v>3389.400000000001</v>
       </c>
       <c r="G85">
         <v>15.6</v>
@@ -8355,28 +8355,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M85">
-        <v>253.85799</v>
+        <v>256.91652</v>
       </c>
       <c r="N85">
-        <v>333.8420099999999</v>
+        <v>330.7834799999999</v>
       </c>
       <c r="O85">
-        <v>30.04578089999999</v>
+        <v>29.77051319999999</v>
       </c>
       <c r="P85">
-        <v>303.7962290999999</v>
+        <v>301.0129667999999</v>
       </c>
       <c r="Q85">
-        <v>699.8962290999999</v>
+        <v>697.1129667999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.24507679916071</v>
+        <v>0.2573256567769052</v>
       </c>
       <c r="T85">
-        <v>2.899720239183233</v>
+        <v>3.077956042277955</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8393,7 +8393,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.315073872600976</v>
+        <v>2.287513469355726</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8401,22 +8401,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09911362508430482</v>
+        <v>0.09931245431128896</v>
       </c>
       <c r="C86">
-        <v>346.6328620758172</v>
+        <v>301.8778684176964</v>
       </c>
       <c r="D86">
-        <v>3720.432862075817</v>
+        <v>3716.027868417696</v>
       </c>
       <c r="E86">
-        <v>2267.9</v>
+        <v>2308.25</v>
       </c>
       <c r="F86">
-        <v>3389.4</v>
+        <v>3429.75</v>
       </c>
       <c r="G86">
         <v>15.6</v>
@@ -8437,28 +8437,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M86">
-        <v>256.91652</v>
+        <v>259.97505</v>
       </c>
       <c r="N86">
-        <v>330.7834799999999</v>
+        <v>327.7249499999999</v>
       </c>
       <c r="O86">
-        <v>29.77051319999999</v>
+        <v>29.49524549999999</v>
       </c>
       <c r="P86">
-        <v>301.0129667999999</v>
+        <v>298.2297044999999</v>
       </c>
       <c r="Q86">
-        <v>697.1129667999999</v>
+        <v>694.3297044999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2573256567769051</v>
+        <v>0.2712076954085929</v>
       </c>
       <c r="T86">
-        <v>3.077956042277953</v>
+        <v>3.279956619118638</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.287513469355726</v>
+        <v>2.260601546186836</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8483,22 +8483,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09931245431128896</v>
+        <v>0.09951128353827308</v>
       </c>
       <c r="C87">
-        <v>301.8778684176964</v>
+        <v>257.1332934515463</v>
       </c>
       <c r="D87">
-        <v>3716.027868417696</v>
+        <v>3711.633293451546</v>
       </c>
       <c r="E87">
-        <v>2308.25</v>
+        <v>2348.6</v>
       </c>
       <c r="F87">
-        <v>3429.75</v>
+        <v>3470.1</v>
       </c>
       <c r="G87">
         <v>15.6</v>
@@ -8519,28 +8519,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M87">
-        <v>259.97505</v>
+        <v>263.03358</v>
       </c>
       <c r="N87">
-        <v>327.7249499999999</v>
+        <v>324.6664199999999</v>
       </c>
       <c r="O87">
-        <v>29.49524549999999</v>
+        <v>29.21997779999999</v>
       </c>
       <c r="P87">
-        <v>298.2297044999999</v>
+        <v>295.4464421999999</v>
       </c>
       <c r="Q87">
-        <v>694.3297044999999</v>
+        <v>691.5464422</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2712076954085929</v>
+        <v>0.2870728824162362</v>
       </c>
       <c r="T87">
-        <v>3.279956619118638</v>
+        <v>3.510814421222278</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.260601546186836</v>
+        <v>2.234315481696291</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8565,22 +8565,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09951128353827308</v>
+        <v>0.09971011276525721</v>
       </c>
       <c r="C88">
-        <v>257.1332934515463</v>
+        <v>212.3991002575876</v>
       </c>
       <c r="D88">
-        <v>3711.633293451546</v>
+        <v>3707.249100257588</v>
       </c>
       <c r="E88">
-        <v>2348.6</v>
+        <v>2388.95</v>
       </c>
       <c r="F88">
-        <v>3470.1</v>
+        <v>3510.45</v>
       </c>
       <c r="G88">
         <v>15.6</v>
@@ -8601,28 +8601,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M88">
-        <v>263.03358</v>
+        <v>266.09211</v>
       </c>
       <c r="N88">
-        <v>324.6664199999999</v>
+        <v>321.6078899999999</v>
       </c>
       <c r="O88">
-        <v>29.21997779999999</v>
+        <v>28.94471009999999</v>
       </c>
       <c r="P88">
-        <v>295.4464421999999</v>
+        <v>292.6631798999999</v>
       </c>
       <c r="Q88">
-        <v>691.5464422</v>
+        <v>688.7631799</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2870728824162362</v>
+        <v>0.3053788674250553</v>
       </c>
       <c r="T88">
-        <v>3.510814421222278</v>
+        <v>3.77718880826494</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8639,7 +8639,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.234315481696291</v>
+        <v>2.208633694550357</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8647,22 +8647,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09971011276525721</v>
+        <v>0.09990894199224132</v>
       </c>
       <c r="C89">
-        <v>212.3991002575876</v>
+        <v>167.6752520902769</v>
       </c>
       <c r="D89">
-        <v>3707.249100257588</v>
+        <v>3702.875252090277</v>
       </c>
       <c r="E89">
-        <v>2388.95</v>
+        <v>2429.3</v>
       </c>
       <c r="F89">
-        <v>3510.45</v>
+        <v>3550.8</v>
       </c>
       <c r="G89">
         <v>15.6</v>
@@ -8683,28 +8683,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M89">
-        <v>266.09211</v>
+        <v>269.15064</v>
       </c>
       <c r="N89">
-        <v>321.6078899999999</v>
+        <v>318.5493599999999</v>
       </c>
       <c r="O89">
-        <v>28.94471009999999</v>
+        <v>28.66944239999999</v>
       </c>
       <c r="P89">
-        <v>292.6631798999999</v>
+        <v>289.8799175999999</v>
       </c>
       <c r="Q89">
-        <v>688.7631799</v>
+        <v>685.9799175999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3053788674250553</v>
+        <v>0.3267358499353443</v>
       </c>
       <c r="T89">
-        <v>3.77718880826494</v>
+        <v>4.087958926481378</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.208633694550357</v>
+        <v>2.183535584385011</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8729,22 +8729,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09990894199224132</v>
+        <v>0.1001077712192255</v>
       </c>
       <c r="C90">
-        <v>167.6752520902769</v>
+        <v>122.9617123772769</v>
       </c>
       <c r="D90">
-        <v>3702.875252090277</v>
+        <v>3698.511712377277</v>
       </c>
       <c r="E90">
-        <v>2429.3</v>
+        <v>2469.65</v>
       </c>
       <c r="F90">
-        <v>3550.8</v>
+        <v>3591.15</v>
       </c>
       <c r="G90">
         <v>15.6</v>
@@ -8765,28 +8765,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M90">
-        <v>269.15064</v>
+        <v>272.20917</v>
       </c>
       <c r="N90">
-        <v>318.5493599999999</v>
+        <v>315.4908299999999</v>
       </c>
       <c r="O90">
-        <v>28.66944239999999</v>
+        <v>28.39417469999999</v>
       </c>
       <c r="P90">
-        <v>289.8799175999999</v>
+        <v>287.0966552999999</v>
       </c>
       <c r="Q90">
-        <v>685.9799175999999</v>
+        <v>683.1966553</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3267358499353443</v>
+        <v>0.3519759201747768</v>
       </c>
       <c r="T90">
-        <v>4.087958926481378</v>
+        <v>4.455232702555351</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.183535584385011</v>
+        <v>2.159001476695292</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8811,22 +8811,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1001077712192255</v>
+        <v>0.1003066004462096</v>
       </c>
       <c r="C91">
-        <v>122.9617123772769</v>
+        <v>78.25844471843675</v>
       </c>
       <c r="D91">
-        <v>3698.511712377277</v>
+        <v>3694.158444718437</v>
       </c>
       <c r="E91">
-        <v>2469.65</v>
+        <v>2510</v>
       </c>
       <c r="F91">
-        <v>3591.15</v>
+        <v>3631.5</v>
       </c>
       <c r="G91">
         <v>15.6</v>
@@ -8847,28 +8847,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M91">
-        <v>272.20917</v>
+        <v>275.2677</v>
       </c>
       <c r="N91">
-        <v>315.4908299999999</v>
+        <v>312.4322999999999</v>
       </c>
       <c r="O91">
-        <v>28.39417469999999</v>
+        <v>28.11890699999999</v>
       </c>
       <c r="P91">
-        <v>287.0966552999999</v>
+        <v>284.3133929999999</v>
       </c>
       <c r="Q91">
-        <v>683.1966553</v>
+        <v>680.4133929999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3519759201747768</v>
+        <v>0.3822640044620958</v>
       </c>
       <c r="T91">
-        <v>4.455232702555351</v>
+        <v>4.895961233844119</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.159001476695292</v>
+        <v>2.135012571398678</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8893,22 +8893,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1003066004462096</v>
+        <v>0.1005054296731937</v>
       </c>
       <c r="C92">
-        <v>78.25844471843675</v>
+        <v>33.56541288478184</v>
       </c>
       <c r="D92">
-        <v>3694.158444718437</v>
+        <v>3689.815412884782</v>
       </c>
       <c r="E92">
-        <v>2510</v>
+        <v>2550.35</v>
       </c>
       <c r="F92">
-        <v>3631.5</v>
+        <v>3671.85</v>
       </c>
       <c r="G92">
         <v>15.6</v>
@@ -8929,28 +8929,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M92">
-        <v>275.2677</v>
+        <v>278.32623</v>
       </c>
       <c r="N92">
-        <v>312.4322999999999</v>
+        <v>309.3737699999999</v>
       </c>
       <c r="O92">
-        <v>28.11890699999999</v>
+        <v>27.84363929999999</v>
       </c>
       <c r="P92">
-        <v>284.3133929999999</v>
+        <v>281.5301306999999</v>
       </c>
       <c r="Q92">
-        <v>680.4133929999999</v>
+        <v>677.6301306999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3822640044620958</v>
+        <v>0.4192827741465968</v>
       </c>
       <c r="T92">
-        <v>4.895961233844119</v>
+        <v>5.434629438752613</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.135012571398678</v>
+        <v>2.111550894789902</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8975,22 +8975,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1005054296731937</v>
+        <v>0.1007042589001778</v>
       </c>
       <c r="C93">
-        <v>33.56541288478184</v>
+        <v>-11.1174191824939</v>
       </c>
       <c r="D93">
-        <v>3689.815412884782</v>
+        <v>3685.482580817506</v>
       </c>
       <c r="E93">
-        <v>2550.35</v>
+        <v>2590.7</v>
       </c>
       <c r="F93">
-        <v>3671.85</v>
+        <v>3712.2</v>
       </c>
       <c r="G93">
         <v>15.6</v>
@@ -9011,28 +9011,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M93">
-        <v>278.32623</v>
+        <v>281.38476</v>
       </c>
       <c r="N93">
-        <v>309.3737699999999</v>
+        <v>306.3152399999999</v>
       </c>
       <c r="O93">
-        <v>27.84363929999999</v>
+        <v>27.56837159999999</v>
       </c>
       <c r="P93">
-        <v>281.5301306999999</v>
+        <v>278.7468683999999</v>
       </c>
       <c r="Q93">
-        <v>677.6301306999999</v>
+        <v>674.8468683999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4192827741465968</v>
+        <v>0.465556236252223</v>
       </c>
       <c r="T93">
-        <v>5.434629438752613</v>
+        <v>6.107964694888231</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -9049,7 +9049,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.111550894789902</v>
+        <v>2.088599254629141</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9057,22 +9057,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1007042589001778</v>
+        <v>0.100903088127162</v>
       </c>
       <c r="C94">
-        <v>-11.1174191824939</v>
+        <v>-55.79008737302229</v>
       </c>
       <c r="D94">
-        <v>3685.482580817506</v>
+        <v>3681.159912626978</v>
       </c>
       <c r="E94">
-        <v>2590.7</v>
+        <v>2631.05</v>
       </c>
       <c r="F94">
-        <v>3712.2</v>
+        <v>3752.55</v>
       </c>
       <c r="G94">
         <v>15.6</v>
@@ -9093,28 +9093,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M94">
-        <v>281.38476</v>
+        <v>284.44329</v>
       </c>
       <c r="N94">
-        <v>306.3152399999999</v>
+        <v>303.2567099999999</v>
       </c>
       <c r="O94">
-        <v>27.56837159999999</v>
+        <v>27.29310389999999</v>
       </c>
       <c r="P94">
-        <v>278.7468683999999</v>
+        <v>275.9636060999999</v>
       </c>
       <c r="Q94">
-        <v>674.8468683999999</v>
+        <v>672.0636060999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.465556236252223</v>
+        <v>0.5250506875308852</v>
       </c>
       <c r="T94">
-        <v>6.107964694888231</v>
+        <v>6.973681452776882</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.088599254629141</v>
+        <v>2.066141198127752</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9139,22 +9139,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.100903088127162</v>
+        <v>0.1011019173541461</v>
       </c>
       <c r="C95">
-        <v>-55.79008737302229</v>
+        <v>-100.452627408255</v>
       </c>
       <c r="D95">
-        <v>3681.159912626978</v>
+        <v>3676.847372591745</v>
       </c>
       <c r="E95">
-        <v>2631.05</v>
+        <v>2671.4</v>
       </c>
       <c r="F95">
-        <v>3752.55</v>
+        <v>3792.9</v>
       </c>
       <c r="G95">
         <v>15.6</v>
@@ -9175,28 +9175,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M95">
-        <v>284.44329</v>
+        <v>287.50182</v>
       </c>
       <c r="N95">
-        <v>303.2567099999999</v>
+        <v>300.1981799999999</v>
       </c>
       <c r="O95">
-        <v>27.29310389999999</v>
+        <v>27.01783619999999</v>
       </c>
       <c r="P95">
-        <v>275.9636060999999</v>
+        <v>273.1803437999999</v>
       </c>
       <c r="Q95">
-        <v>672.0636060999999</v>
+        <v>669.2803438</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5250506875308852</v>
+        <v>0.6043766225691017</v>
       </c>
       <c r="T95">
-        <v>6.973681452776882</v>
+        <v>8.127970463295085</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9213,7 +9213,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.066141198127752</v>
+        <v>2.044160972615756</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9221,22 +9221,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1011019173541461</v>
+        <v>0.1013007465811302</v>
       </c>
       <c r="C96">
-        <v>-100.452627408255</v>
+        <v>-145.1050748424482</v>
       </c>
       <c r="D96">
-        <v>3676.847372591745</v>
+        <v>3672.544925157552</v>
       </c>
       <c r="E96">
-        <v>2671.4</v>
+        <v>2711.75</v>
       </c>
       <c r="F96">
-        <v>3792.9</v>
+        <v>3833.25</v>
       </c>
       <c r="G96">
         <v>15.6</v>
@@ -9257,28 +9257,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M96">
-        <v>287.50182</v>
+        <v>290.5603500000001</v>
       </c>
       <c r="N96">
-        <v>300.1981799999999</v>
+        <v>297.1396499999998</v>
       </c>
       <c r="O96">
-        <v>27.01783619999999</v>
+        <v>26.74256849999999</v>
       </c>
       <c r="P96">
-        <v>273.1803437999999</v>
+        <v>270.3970814999998</v>
       </c>
       <c r="Q96">
-        <v>669.2803438</v>
+        <v>666.4970814999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6043766225691017</v>
+        <v>0.7154329316226049</v>
       </c>
       <c r="T96">
-        <v>8.127970463295085</v>
+        <v>9.743975078020572</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.044160972615756</v>
+        <v>2.022643488693484</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9303,22 +9303,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1013007465811302</v>
+        <v>0.1014995758081143</v>
       </c>
       <c r="C97">
-        <v>-145.1050748424482</v>
+        <v>-189.7474650636341</v>
       </c>
       <c r="D97">
-        <v>3672.544925157552</v>
+        <v>3668.252534936366</v>
       </c>
       <c r="E97">
-        <v>2711.75</v>
+        <v>2752.1</v>
       </c>
       <c r="F97">
-        <v>3833.25</v>
+        <v>3873.6</v>
       </c>
       <c r="G97">
         <v>15.6</v>
@@ -9339,28 +9339,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M97">
-        <v>290.5603500000001</v>
+        <v>293.61888</v>
       </c>
       <c r="N97">
-        <v>297.1396499999998</v>
+        <v>294.0811199999999</v>
       </c>
       <c r="O97">
-        <v>26.74256849999999</v>
+        <v>26.46730079999999</v>
       </c>
       <c r="P97">
-        <v>270.3970814999998</v>
+        <v>267.6138191999999</v>
       </c>
       <c r="Q97">
-        <v>666.4970814999999</v>
+        <v>663.7138192</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7154329316226049</v>
+        <v>0.8820173952028596</v>
       </c>
       <c r="T97">
-        <v>9.743975078020572</v>
+        <v>12.1679820001088</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.022643488693484</v>
+        <v>2.00157428568626</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9385,22 +9385,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1014995758081143</v>
+        <v>0.1142327450350984</v>
       </c>
       <c r="C98">
-        <v>-189.7474650636336</v>
+        <v>-485.5439739070089</v>
       </c>
       <c r="D98">
-        <v>3668.252534936366</v>
+        <v>3412.806026092991</v>
       </c>
       <c r="E98">
-        <v>2752.1</v>
+        <v>2792.45</v>
       </c>
       <c r="F98">
-        <v>3873.6</v>
+        <v>3913.95</v>
       </c>
       <c r="G98">
         <v>15.6</v>
@@ -9421,45 +9421,45 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M98">
-        <v>293.61888</v>
+        <v>352.2555</v>
       </c>
       <c r="N98">
-        <v>294.0811199999999</v>
+        <v>235.4444999999999</v>
       </c>
       <c r="O98">
-        <v>26.46730079999999</v>
+        <v>21.190005</v>
       </c>
       <c r="P98">
-        <v>267.6138192</v>
+        <v>214.254495</v>
       </c>
       <c r="Q98">
-        <v>663.7138192</v>
+        <v>610.354495</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8820173952028574</v>
+        <v>1.159658167836614</v>
       </c>
       <c r="T98">
-        <v>12.16798200010877</v>
+        <v>16.20799353692246</v>
       </c>
       <c r="U98">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V98">
         <v>0.09</v>
       </c>
       <c r="W98">
-        <v>0.06897800000000001</v>
+        <v>0.0819</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y98">
-        <v>2.001574285686261</v>
+        <v>1.668391267134225</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9467,22 +9467,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1142327450350984</v>
+        <v>0.1145607942620826</v>
       </c>
       <c r="C99">
-        <v>-485.5439739070089</v>
+        <v>-532.0058760814936</v>
       </c>
       <c r="D99">
-        <v>3412.806026092991</v>
+        <v>3406.694123918506</v>
       </c>
       <c r="E99">
-        <v>2792.45</v>
+        <v>2832.8</v>
       </c>
       <c r="F99">
-        <v>3913.95</v>
+        <v>3954.3</v>
       </c>
       <c r="G99">
         <v>15.6</v>
@@ -9503,28 +9503,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M99">
-        <v>352.2555</v>
+        <v>355.8869999999999</v>
       </c>
       <c r="N99">
-        <v>235.4444999999999</v>
+        <v>231.813</v>
       </c>
       <c r="O99">
-        <v>21.190005</v>
+        <v>20.86317</v>
       </c>
       <c r="P99">
-        <v>214.254495</v>
+        <v>210.94983</v>
       </c>
       <c r="Q99">
-        <v>610.354495</v>
+        <v>607.04983</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.159658167836614</v>
+        <v>1.714939713104127</v>
       </c>
       <c r="T99">
-        <v>16.20799353692246</v>
+        <v>24.28801661054985</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9541,7 +9541,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.668391267134225</v>
+        <v>1.651366866449182</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9549,22 +9549,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1145607942620826</v>
+        <v>0.1148888434890667</v>
       </c>
       <c r="C100">
-        <v>-532.0058760814936</v>
+        <v>-578.4459261092038</v>
       </c>
       <c r="D100">
-        <v>3406.694123918506</v>
+        <v>3400.604073890796</v>
       </c>
       <c r="E100">
-        <v>2832.8</v>
+        <v>2873.15</v>
       </c>
       <c r="F100">
-        <v>3954.3</v>
+        <v>3994.65</v>
       </c>
       <c r="G100">
         <v>15.6</v>
@@ -9585,28 +9585,28 @@
         <v>587.6999999999999</v>
       </c>
       <c r="M100">
-        <v>355.8869999999999</v>
+        <v>359.5185</v>
       </c>
       <c r="N100">
-        <v>231.813</v>
+        <v>228.1814999999999</v>
       </c>
       <c r="O100">
-        <v>20.86317</v>
+        <v>20.53633499999999</v>
       </c>
       <c r="P100">
-        <v>210.94983</v>
+        <v>207.6451649999999</v>
       </c>
       <c r="Q100">
-        <v>607.04983</v>
+        <v>603.7451649999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.714939713104127</v>
+        <v>3.380784348906667</v>
       </c>
       <c r="T100">
-        <v>24.28801661054985</v>
+        <v>48.52808583143203</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9623,91 +9623,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.651366866449182</v>
+        <v>1.634686393050705</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1148888434890667</v>
-      </c>
-      <c r="C101">
-        <v>-578.4459261092038</v>
-      </c>
-      <c r="D101">
-        <v>3400.604073890796</v>
-      </c>
-      <c r="E101">
-        <v>2873.15</v>
-      </c>
-      <c r="F101">
-        <v>3994.65</v>
-      </c>
-      <c r="G101">
-        <v>15.6</v>
-      </c>
-      <c r="H101">
-        <v>2913.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>983.8</v>
-      </c>
-      <c r="K101">
-        <v>396.1</v>
-      </c>
-      <c r="L101">
-        <v>587.6999999999999</v>
-      </c>
-      <c r="M101">
-        <v>359.5185</v>
-      </c>
-      <c r="N101">
-        <v>228.1814999999999</v>
-      </c>
-      <c r="O101">
-        <v>20.53633499999999</v>
-      </c>
-      <c r="P101">
-        <v>207.6451649999999</v>
-      </c>
-      <c r="Q101">
-        <v>603.7451649999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.380784348906667</v>
-      </c>
-      <c r="T101">
-        <v>48.52808583143203</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.09</v>
-      </c>
-      <c r="W101">
-        <v>0.0819</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.634686393050705</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
